--- a/Libro de codigos.xlsx
+++ b/Libro de codigos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luis_\Desktop\github\CATALINA_PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1975620-C4BE-4CF7-A320-48B3D1FB0C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CCCD70-0A44-424B-A80D-79C22ACA7D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -2909,18 +2909,12 @@
       <name val="&quot;Open Sans&quot;"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2968,35 +2962,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3222,3896 +3221,3896 @@
     <col min="2" max="2" width="71.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="19" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="19" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+    </row>
+    <row r="8" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:26" s="22" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A11" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+    </row>
+    <row r="13" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A15" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A16" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="6"/>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+    </row>
+    <row r="18" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+    </row>
+    <row r="19" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A19" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A21" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="12.5">
-      <c r="A22" s="10" t="s">
+    <row r="22" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-    </row>
-    <row r="23" spans="1:26" ht="12.5">
-      <c r="A23" s="11" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+    </row>
+    <row r="23" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A23" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="12.5">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A24" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="12.5">
-      <c r="A25" s="12" t="s">
+    <row r="25" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-    </row>
-    <row r="26" spans="1:26" ht="12.5">
-      <c r="A26" s="11" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+    </row>
+    <row r="26" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A26" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="12.5">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A27" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="12.5">
-      <c r="A28" s="11" t="s">
+    <row r="28" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A28" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="12.5">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A29" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="10" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="12.5">
-      <c r="A30" s="12" t="s">
+    <row r="30" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A30" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-    </row>
-    <row r="31" spans="1:26" ht="12.5">
-      <c r="A31" s="11" t="s">
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+    </row>
+    <row r="31" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A31" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="12.5">
-      <c r="A32" s="11" t="s">
+    <row r="32" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A32" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="12.5">
-      <c r="A33" s="11" t="s">
+    <row r="33" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A33" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="12.5">
-      <c r="A34" s="11" t="s">
+    <row r="34" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A34" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="12.5">
-      <c r="A35" s="11" t="s">
+    <row r="35" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A35" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="12.5">
-      <c r="A36" s="11" t="s">
+    <row r="36" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A36" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="12.5">
-      <c r="A37" s="11" t="s">
+    <row r="37" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A37" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="12.5">
-      <c r="A38" s="11" t="s">
+    <row r="38" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A38" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="12.5">
-      <c r="A39" s="10" t="s">
+    <row r="39" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A39" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-    </row>
-    <row r="40" spans="1:26" ht="12.5">
-      <c r="A40" s="10" t="s">
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+    </row>
+    <row r="40" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A40" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6"/>
-      <c r="W40" s="6"/>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="6"/>
-      <c r="Z40" s="6"/>
-    </row>
-    <row r="41" spans="1:26" ht="12.5">
-      <c r="A41" s="9" t="s">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+    </row>
+    <row r="41" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A41" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="12.5">
-      <c r="A42" s="9" t="s">
+    <row r="42" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="12.5">
-      <c r="A43" s="9" t="s">
+    <row r="43" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A43" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="12.5">
-      <c r="A44" s="9" t="s">
+    <row r="44" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A44" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="12.5">
-      <c r="A45" s="9" t="s">
+    <row r="45" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A45" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="10" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="12.5">
-      <c r="A46" s="9" t="s">
+    <row r="46" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A46" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="12.5">
-      <c r="A47" s="9" t="s">
+    <row r="47" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A47" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="10" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="12.5">
-      <c r="A48" s="9" t="s">
+    <row r="48" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A48" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="10" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="12.5">
-      <c r="A49" s="9" t="s">
+    <row r="49" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A49" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="10" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="12.5">
-      <c r="A50" s="11" t="s">
+    <row r="50" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A50" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="21" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="12.5">
-      <c r="A51" s="12" t="s">
+    <row r="51" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A51" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-    </row>
-    <row r="52" spans="1:26" ht="12.5">
-      <c r="A52" s="12" t="s">
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+    </row>
+    <row r="52" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A52" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="6"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
-    </row>
-    <row r="53" spans="1:26" ht="12.5">
-      <c r="A53" s="10" t="s">
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+    </row>
+    <row r="53" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A53" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-    </row>
-    <row r="54" spans="1:26" ht="12.5">
-      <c r="A54" s="9" t="s">
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+    </row>
+    <row r="54" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A54" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="12.5">
-      <c r="A55" s="9" t="s">
+    <row r="55" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A55" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="12.5">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A56" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="10" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="12.5">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A57" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="12.5">
-      <c r="A58" s="9" t="s">
+    <row r="58" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A58" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="10" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="12.5">
-      <c r="A59" s="10" t="s">
+    <row r="59" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A59" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6"/>
-      <c r="T59" s="6"/>
-      <c r="U59" s="6"/>
-      <c r="V59" s="6"/>
-      <c r="W59" s="6"/>
-      <c r="X59" s="6"/>
-      <c r="Y59" s="6"/>
-      <c r="Z59" s="6"/>
-    </row>
-    <row r="60" spans="1:26" ht="12.5">
-      <c r="A60" s="10" t="s">
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+    </row>
+    <row r="60" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A60" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
-      <c r="X60" s="6"/>
-      <c r="Y60" s="6"/>
-      <c r="Z60" s="6"/>
-    </row>
-    <row r="61" spans="1:26" ht="12.5">
-      <c r="A61" s="10" t="s">
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+    </row>
+    <row r="61" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A61" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="6"/>
-      <c r="T61" s="6"/>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="6"/>
-      <c r="Y61" s="6"/>
-      <c r="Z61" s="6"/>
-    </row>
-    <row r="62" spans="1:26" ht="12.5">
-      <c r="A62" s="10" t="s">
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A62" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="6"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-    </row>
-    <row r="63" spans="1:26" ht="12.5">
-      <c r="A63" s="10" t="s">
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+    </row>
+    <row r="63" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A63" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-      <c r="T63" s="6"/>
-      <c r="U63" s="6"/>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
-      <c r="Y63" s="6"/>
-      <c r="Z63" s="6"/>
-    </row>
-    <row r="64" spans="1:26" ht="12.5">
-      <c r="A64" s="10" t="s">
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+    </row>
+    <row r="64" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A64" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
-      <c r="X64" s="6"/>
-      <c r="Y64" s="6"/>
-      <c r="Z64" s="6"/>
-    </row>
-    <row r="65" spans="1:26" ht="12.5">
-      <c r="A65" s="10" t="s">
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+    </row>
+    <row r="65" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A65" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6"/>
-      <c r="T65" s="6"/>
-      <c r="U65" s="6"/>
-      <c r="V65" s="6"/>
-      <c r="W65" s="6"/>
-      <c r="X65" s="6"/>
-      <c r="Y65" s="6"/>
-      <c r="Z65" s="6"/>
-    </row>
-    <row r="66" spans="1:26" ht="12.5">
-      <c r="A66" s="11" t="s">
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+    </row>
+    <row r="66" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A66" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="10" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="12.5">
-      <c r="A67" s="11" t="s">
+    <row r="67" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A67" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="12.5">
-      <c r="A68" s="11" t="s">
+    <row r="68" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A68" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="12.5">
-      <c r="A69" s="11" t="s">
+    <row r="69" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A69" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="12.5">
-      <c r="A70" s="11" t="s">
+    <row r="70" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A70" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="10" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="12.5">
-      <c r="A71" s="11" t="s">
+    <row r="71" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A71" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="10" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="12.5">
-      <c r="A72" s="12" t="s">
+    <row r="72" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A72" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
-      <c r="V72" s="6"/>
-      <c r="W72" s="6"/>
-      <c r="X72" s="6"/>
-      <c r="Y72" s="6"/>
-      <c r="Z72" s="6"/>
-    </row>
-    <row r="73" spans="1:26" ht="12.5">
-      <c r="A73" s="11" t="s">
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+    </row>
+    <row r="73" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A73" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="12.5">
-      <c r="A74" s="11" t="s">
+    <row r="74" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A74" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="12.5">
-      <c r="A75" s="11" t="s">
+    <row r="75" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A75" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="12.5">
-      <c r="A76" s="9" t="s">
+    <row r="76" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A76" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="12.5">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A77" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="12.5">
-      <c r="A78" s="9" t="s">
+    <row r="78" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A78" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="12.5">
-      <c r="A79" s="11" t="s">
+    <row r="79" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A79" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="12.5">
-      <c r="A80" s="9" t="s">
+    <row r="80" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A80" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="12.5">
-      <c r="A81" s="9" t="s">
+    <row r="81" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A81" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="12.5">
-      <c r="A82" s="9" t="s">
+    <row r="82" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A82" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="12.5">
-      <c r="A83" s="9" t="s">
+    <row r="83" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A83" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="12.5">
-      <c r="A84" s="9" t="s">
+    <row r="84" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A84" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="21" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="12.5">
-      <c r="A85" s="9" t="s">
+    <row r="85" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A85" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="21" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="12.5">
-      <c r="A86" s="9" t="s">
+    <row r="86" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A86" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="21" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="12.5">
-      <c r="A87" s="11" t="s">
+    <row r="87" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A87" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="21" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="12.5">
-      <c r="A88" s="11" t="s">
+    <row r="88" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A88" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="21" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="12.5">
-      <c r="A89" s="11" t="s">
+    <row r="89" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A89" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="12.5">
-      <c r="A90" s="11" t="s">
+    <row r="90" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A90" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="21" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="12.5">
-      <c r="A91" s="11" t="s">
+    <row r="91" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A91" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="12.5">
-      <c r="A92" s="11" t="s">
+    <row r="92" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A92" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="12.5">
-      <c r="A93" s="11" t="s">
+    <row r="93" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A93" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="12.5">
-      <c r="A94" s="11" t="s">
+    <row r="94" spans="1:3" s="12" customFormat="1" ht="12.5">
+      <c r="A94" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="10" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="12.5">
-      <c r="A95" s="11" t="s">
+    <row r="95" spans="1:3" s="12" customFormat="1" ht="12.5">
+      <c r="A95" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="12.5">
-      <c r="A96" s="11" t="s">
+    <row r="96" spans="1:3" s="22" customFormat="1" ht="12.5">
+      <c r="A96" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="12.5">
-      <c r="A97" s="11" t="s">
+    <row r="97" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A97" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="12.5">
-      <c r="A98" s="11" t="s">
+    <row r="98" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A98" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="12.5">
-      <c r="A99" s="11" t="s">
+    <row r="99" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A99" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="12.5">
-      <c r="A100" s="9" t="s">
+    <row r="100" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A100" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="12.5">
-      <c r="A101" s="9" t="s">
+    <row r="101" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A101" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="12.5">
-      <c r="A102" s="9" t="s">
+    <row r="102" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A102" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="12.5">
-      <c r="A103" s="9" t="s">
+    <row r="103" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A103" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="12.5">
-      <c r="A104" s="9" t="s">
+    <row r="104" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A104" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="12.5">
-      <c r="A105" s="9" t="s">
+    <row r="105" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A105" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="21" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="12.5">
-      <c r="A106" s="9" t="s">
+    <row r="106" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A106" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="12.5">
-      <c r="A107" s="11" t="s">
+    <row r="107" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A107" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="21" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="12.5">
-      <c r="A108" s="11" t="s">
+    <row r="108" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A108" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="12.5">
-      <c r="A109" s="11" t="s">
+    <row r="109" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A109" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="12.5">
-      <c r="A110" s="11" t="s">
+    <row r="110" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A110" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="12.5">
-      <c r="A111" s="11" t="s">
+    <row r="111" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A111" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="12.5">
-      <c r="A112" s="11" t="s">
+    <row r="112" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A112" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="21" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="12.5">
-      <c r="A113" s="11" t="s">
+    <row r="113" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A113" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="12.5">
-      <c r="A114" s="11" t="s">
+    <row r="114" spans="1:2" s="12" customFormat="1" ht="12.5">
+      <c r="A114" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="10" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="12.5">
-      <c r="A115" s="11" t="s">
+    <row r="115" spans="1:2" s="12" customFormat="1" ht="12.5">
+      <c r="A115" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="12.5">
-      <c r="A116" s="9" t="s">
+    <row r="116" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A116" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="12.5">
-      <c r="A117" s="9" t="s">
+    <row r="117" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A117" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="12.5">
-      <c r="A118" s="9" t="s">
+    <row r="118" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A118" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="12.5">
-      <c r="A119" s="11" t="s">
+    <row r="119" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A119" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="12.5">
-      <c r="A120" s="9" t="s">
+    <row r="120" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A120" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="12.5">
-      <c r="A121" s="9" t="s">
+    <row r="121" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A121" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="12.5">
-      <c r="A122" s="9" t="s">
+    <row r="122" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A122" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="12.5">
-      <c r="A123" s="9" t="s">
+    <row r="123" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A123" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="12.5">
-      <c r="A124" s="9" t="s">
+    <row r="124" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A124" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="12.5">
-      <c r="A125" s="9" t="s">
+    <row r="125" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A125" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="21" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="12.5">
-      <c r="A126" s="9" t="s">
+    <row r="126" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A126" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="12.5">
-      <c r="A127" s="11" t="s">
+    <row r="127" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A127" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="21" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="12.5">
-      <c r="A128" s="11" t="s">
+    <row r="128" spans="1:2" s="22" customFormat="1" ht="12.5">
+      <c r="A128" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="129" spans="1:26" ht="12.5">
-      <c r="A129" s="11" t="s">
+    <row r="129" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A129" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="130" spans="1:26" ht="12.5">
-      <c r="A130" s="11" t="s">
+    <row r="130" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A130" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:26" ht="12.5">
-      <c r="A131" s="11" t="s">
+    <row r="131" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A131" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:26" ht="12.5">
-      <c r="A132" s="11" t="s">
+    <row r="132" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A132" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="21" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="133" spans="1:26" ht="12.5">
-      <c r="A133" s="11" t="s">
+    <row r="133" spans="1:26" s="22" customFormat="1" ht="12.5">
+      <c r="A133" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:26" ht="12.5">
-      <c r="A134" s="1" t="s">
+    <row r="134" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A134" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="135" spans="1:26" ht="12.5">
-      <c r="A135" s="1" t="s">
+    <row r="135" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A135" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" s="10" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="136" spans="1:26" ht="12.5">
-      <c r="A136" s="6" t="s">
+    <row r="136" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A136" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
-      <c r="M136" s="6"/>
-      <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
-      <c r="P136" s="6"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="6"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="6"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-    </row>
-    <row r="137" spans="1:26" ht="12.5">
-      <c r="A137" s="6" t="s">
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+      <c r="L136" s="4"/>
+      <c r="M136" s="4"/>
+      <c r="N136" s="4"/>
+      <c r="O136" s="4"/>
+      <c r="P136" s="4"/>
+      <c r="Q136" s="4"/>
+      <c r="R136" s="4"/>
+      <c r="S136" s="4"/>
+      <c r="T136" s="4"/>
+      <c r="U136" s="4"/>
+      <c r="V136" s="4"/>
+      <c r="W136" s="4"/>
+      <c r="X136" s="4"/>
+      <c r="Y136" s="4"/>
+      <c r="Z136" s="4"/>
+    </row>
+    <row r="137" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A137" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
-      <c r="M137" s="6"/>
-      <c r="N137" s="6"/>
-      <c r="O137" s="6"/>
-      <c r="P137" s="6"/>
-      <c r="Q137" s="6"/>
-      <c r="R137" s="6"/>
-      <c r="S137" s="6"/>
-      <c r="T137" s="6"/>
-      <c r="U137" s="6"/>
-      <c r="V137" s="6"/>
-      <c r="W137" s="6"/>
-      <c r="X137" s="6"/>
-      <c r="Y137" s="6"/>
-      <c r="Z137" s="6"/>
-    </row>
-    <row r="138" spans="1:26" ht="12.5">
-      <c r="A138" s="6" t="s">
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
+      <c r="L137" s="4"/>
+      <c r="M137" s="4"/>
+      <c r="N137" s="4"/>
+      <c r="O137" s="4"/>
+      <c r="P137" s="4"/>
+      <c r="Q137" s="4"/>
+      <c r="R137" s="4"/>
+      <c r="S137" s="4"/>
+      <c r="T137" s="4"/>
+      <c r="U137" s="4"/>
+      <c r="V137" s="4"/>
+      <c r="W137" s="4"/>
+      <c r="X137" s="4"/>
+      <c r="Y137" s="4"/>
+      <c r="Z137" s="4"/>
+    </row>
+    <row r="138" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A138" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="6"/>
-      <c r="N138" s="6"/>
-      <c r="O138" s="6"/>
-      <c r="P138" s="6"/>
-      <c r="Q138" s="6"/>
-      <c r="R138" s="6"/>
-      <c r="S138" s="6"/>
-      <c r="T138" s="6"/>
-      <c r="U138" s="6"/>
-      <c r="V138" s="6"/>
-      <c r="W138" s="6"/>
-      <c r="X138" s="6"/>
-      <c r="Y138" s="6"/>
-      <c r="Z138" s="6"/>
-    </row>
-    <row r="139" spans="1:26" ht="12.5">
-      <c r="A139" s="6" t="s">
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+      <c r="L138" s="4"/>
+      <c r="M138" s="4"/>
+      <c r="N138" s="4"/>
+      <c r="O138" s="4"/>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="4"/>
+      <c r="R138" s="4"/>
+      <c r="S138" s="4"/>
+      <c r="T138" s="4"/>
+      <c r="U138" s="4"/>
+      <c r="V138" s="4"/>
+      <c r="W138" s="4"/>
+      <c r="X138" s="4"/>
+      <c r="Y138" s="4"/>
+      <c r="Z138" s="4"/>
+    </row>
+    <row r="139" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A139" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B139" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
-      <c r="M139" s="6"/>
-      <c r="N139" s="6"/>
-      <c r="O139" s="6"/>
-      <c r="P139" s="6"/>
-      <c r="Q139" s="6"/>
-      <c r="R139" s="6"/>
-      <c r="S139" s="6"/>
-      <c r="T139" s="6"/>
-      <c r="U139" s="6"/>
-      <c r="V139" s="6"/>
-      <c r="W139" s="6"/>
-      <c r="X139" s="6"/>
-      <c r="Y139" s="6"/>
-      <c r="Z139" s="6"/>
-    </row>
-    <row r="140" spans="1:26" ht="12.5">
-      <c r="A140" s="6" t="s">
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+      <c r="L139" s="4"/>
+      <c r="M139" s="4"/>
+      <c r="N139" s="4"/>
+      <c r="O139" s="4"/>
+      <c r="P139" s="4"/>
+      <c r="Q139" s="4"/>
+      <c r="R139" s="4"/>
+      <c r="S139" s="4"/>
+      <c r="T139" s="4"/>
+      <c r="U139" s="4"/>
+      <c r="V139" s="4"/>
+      <c r="W139" s="4"/>
+      <c r="X139" s="4"/>
+      <c r="Y139" s="4"/>
+      <c r="Z139" s="4"/>
+    </row>
+    <row r="140" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A140" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
-      <c r="M140" s="6"/>
-      <c r="N140" s="6"/>
-      <c r="O140" s="6"/>
-      <c r="P140" s="6"/>
-      <c r="Q140" s="6"/>
-      <c r="R140" s="6"/>
-      <c r="S140" s="6"/>
-      <c r="T140" s="6"/>
-      <c r="U140" s="6"/>
-      <c r="V140" s="6"/>
-      <c r="W140" s="6"/>
-      <c r="X140" s="6"/>
-      <c r="Y140" s="6"/>
-      <c r="Z140" s="6"/>
-    </row>
-    <row r="141" spans="1:26" ht="12.5">
-      <c r="A141" s="6" t="s">
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="4"/>
+      <c r="L140" s="4"/>
+      <c r="M140" s="4"/>
+      <c r="N140" s="4"/>
+      <c r="O140" s="4"/>
+      <c r="P140" s="4"/>
+      <c r="Q140" s="4"/>
+      <c r="R140" s="4"/>
+      <c r="S140" s="4"/>
+      <c r="T140" s="4"/>
+      <c r="U140" s="4"/>
+      <c r="V140" s="4"/>
+      <c r="W140" s="4"/>
+      <c r="X140" s="4"/>
+      <c r="Y140" s="4"/>
+      <c r="Z140" s="4"/>
+    </row>
+    <row r="141" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A141" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
-      <c r="L141" s="6"/>
-      <c r="M141" s="6"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="6"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="6"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="6"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-    </row>
-    <row r="142" spans="1:26" ht="12.5">
-      <c r="A142" s="6" t="s">
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
+      <c r="L141" s="4"/>
+      <c r="M141" s="4"/>
+      <c r="N141" s="4"/>
+      <c r="O141" s="4"/>
+      <c r="P141" s="4"/>
+      <c r="Q141" s="4"/>
+      <c r="R141" s="4"/>
+      <c r="S141" s="4"/>
+      <c r="T141" s="4"/>
+      <c r="U141" s="4"/>
+      <c r="V141" s="4"/>
+      <c r="W141" s="4"/>
+      <c r="X141" s="4"/>
+      <c r="Y141" s="4"/>
+      <c r="Z141" s="4"/>
+    </row>
+    <row r="142" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A142" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B142" s="6" t="s">
+      <c r="B142" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
-      <c r="L142" s="6"/>
-      <c r="M142" s="6"/>
-      <c r="N142" s="6"/>
-      <c r="O142" s="6"/>
-      <c r="P142" s="6"/>
-      <c r="Q142" s="6"/>
-      <c r="R142" s="6"/>
-      <c r="S142" s="6"/>
-      <c r="T142" s="6"/>
-      <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
-      <c r="W142" s="6"/>
-      <c r="X142" s="6"/>
-      <c r="Y142" s="6"/>
-      <c r="Z142" s="6"/>
-    </row>
-    <row r="143" spans="1:26" ht="12.5">
-      <c r="A143" s="6" t="s">
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+      <c r="L142" s="4"/>
+      <c r="M142" s="4"/>
+      <c r="N142" s="4"/>
+      <c r="O142" s="4"/>
+      <c r="P142" s="4"/>
+      <c r="Q142" s="4"/>
+      <c r="R142" s="4"/>
+      <c r="S142" s="4"/>
+      <c r="T142" s="4"/>
+      <c r="U142" s="4"/>
+      <c r="V142" s="4"/>
+      <c r="W142" s="4"/>
+      <c r="X142" s="4"/>
+      <c r="Y142" s="4"/>
+      <c r="Z142" s="4"/>
+    </row>
+    <row r="143" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A143" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
-      <c r="L143" s="6"/>
-      <c r="M143" s="6"/>
-      <c r="N143" s="6"/>
-      <c r="O143" s="6"/>
-      <c r="P143" s="6"/>
-      <c r="Q143" s="6"/>
-      <c r="R143" s="6"/>
-      <c r="S143" s="6"/>
-      <c r="T143" s="6"/>
-      <c r="U143" s="6"/>
-      <c r="V143" s="6"/>
-      <c r="W143" s="6"/>
-      <c r="X143" s="6"/>
-      <c r="Y143" s="6"/>
-      <c r="Z143" s="6"/>
-    </row>
-    <row r="144" spans="1:26" ht="12.5">
-      <c r="A144" s="6" t="s">
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+      <c r="L143" s="4"/>
+      <c r="M143" s="4"/>
+      <c r="N143" s="4"/>
+      <c r="O143" s="4"/>
+      <c r="P143" s="4"/>
+      <c r="Q143" s="4"/>
+      <c r="R143" s="4"/>
+      <c r="S143" s="4"/>
+      <c r="T143" s="4"/>
+      <c r="U143" s="4"/>
+      <c r="V143" s="4"/>
+      <c r="W143" s="4"/>
+      <c r="X143" s="4"/>
+      <c r="Y143" s="4"/>
+      <c r="Z143" s="4"/>
+    </row>
+    <row r="144" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A144" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B144" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6"/>
-      <c r="L144" s="6"/>
-      <c r="M144" s="6"/>
-      <c r="N144" s="6"/>
-      <c r="O144" s="6"/>
-      <c r="P144" s="6"/>
-      <c r="Q144" s="6"/>
-      <c r="R144" s="6"/>
-      <c r="S144" s="6"/>
-      <c r="T144" s="6"/>
-      <c r="U144" s="6"/>
-      <c r="V144" s="6"/>
-      <c r="W144" s="6"/>
-      <c r="X144" s="6"/>
-      <c r="Y144" s="6"/>
-      <c r="Z144" s="6"/>
-    </row>
-    <row r="145" spans="1:26" ht="12.5">
-      <c r="A145" s="6" t="s">
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+      <c r="L144" s="4"/>
+      <c r="M144" s="4"/>
+      <c r="N144" s="4"/>
+      <c r="O144" s="4"/>
+      <c r="P144" s="4"/>
+      <c r="Q144" s="4"/>
+      <c r="R144" s="4"/>
+      <c r="S144" s="4"/>
+      <c r="T144" s="4"/>
+      <c r="U144" s="4"/>
+      <c r="V144" s="4"/>
+      <c r="W144" s="4"/>
+      <c r="X144" s="4"/>
+      <c r="Y144" s="4"/>
+      <c r="Z144" s="4"/>
+    </row>
+    <row r="145" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A145" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B145" s="6" t="s">
+      <c r="B145" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="6"/>
-      <c r="L145" s="6"/>
-      <c r="M145" s="6"/>
-      <c r="N145" s="6"/>
-      <c r="O145" s="6"/>
-      <c r="P145" s="6"/>
-      <c r="Q145" s="6"/>
-      <c r="R145" s="6"/>
-      <c r="S145" s="6"/>
-      <c r="T145" s="6"/>
-      <c r="U145" s="6"/>
-      <c r="V145" s="6"/>
-      <c r="W145" s="6"/>
-      <c r="X145" s="6"/>
-      <c r="Y145" s="6"/>
-      <c r="Z145" s="6"/>
-    </row>
-    <row r="146" spans="1:26" ht="12.5">
-      <c r="A146" s="6" t="s">
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+      <c r="L145" s="4"/>
+      <c r="M145" s="4"/>
+      <c r="N145" s="4"/>
+      <c r="O145" s="4"/>
+      <c r="P145" s="4"/>
+      <c r="Q145" s="4"/>
+      <c r="R145" s="4"/>
+      <c r="S145" s="4"/>
+      <c r="T145" s="4"/>
+      <c r="U145" s="4"/>
+      <c r="V145" s="4"/>
+      <c r="W145" s="4"/>
+      <c r="X145" s="4"/>
+      <c r="Y145" s="4"/>
+      <c r="Z145" s="4"/>
+    </row>
+    <row r="146" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A146" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B146" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="6"/>
-      <c r="L146" s="6"/>
-      <c r="M146" s="6"/>
-      <c r="N146" s="6"/>
-      <c r="O146" s="6"/>
-      <c r="P146" s="6"/>
-      <c r="Q146" s="6"/>
-      <c r="R146" s="6"/>
-      <c r="S146" s="6"/>
-      <c r="T146" s="6"/>
-      <c r="U146" s="6"/>
-      <c r="V146" s="6"/>
-      <c r="W146" s="6"/>
-      <c r="X146" s="6"/>
-      <c r="Y146" s="6"/>
-      <c r="Z146" s="6"/>
-    </row>
-    <row r="147" spans="1:26" ht="12.5">
-      <c r="A147" s="6" t="s">
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
+      <c r="L146" s="4"/>
+      <c r="M146" s="4"/>
+      <c r="N146" s="4"/>
+      <c r="O146" s="4"/>
+      <c r="P146" s="4"/>
+      <c r="Q146" s="4"/>
+      <c r="R146" s="4"/>
+      <c r="S146" s="4"/>
+      <c r="T146" s="4"/>
+      <c r="U146" s="4"/>
+      <c r="V146" s="4"/>
+      <c r="W146" s="4"/>
+      <c r="X146" s="4"/>
+      <c r="Y146" s="4"/>
+      <c r="Z146" s="4"/>
+    </row>
+    <row r="147" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A147" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B147" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
-      <c r="L147" s="6"/>
-      <c r="M147" s="6"/>
-      <c r="N147" s="6"/>
-      <c r="O147" s="6"/>
-      <c r="P147" s="6"/>
-      <c r="Q147" s="6"/>
-      <c r="R147" s="6"/>
-      <c r="S147" s="6"/>
-      <c r="T147" s="6"/>
-      <c r="U147" s="6"/>
-      <c r="V147" s="6"/>
-      <c r="W147" s="6"/>
-      <c r="X147" s="6"/>
-      <c r="Y147" s="6"/>
-      <c r="Z147" s="6"/>
-    </row>
-    <row r="148" spans="1:26" ht="12.5">
-      <c r="A148" s="6" t="s">
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
+      <c r="L147" s="4"/>
+      <c r="M147" s="4"/>
+      <c r="N147" s="4"/>
+      <c r="O147" s="4"/>
+      <c r="P147" s="4"/>
+      <c r="Q147" s="4"/>
+      <c r="R147" s="4"/>
+      <c r="S147" s="4"/>
+      <c r="T147" s="4"/>
+      <c r="U147" s="4"/>
+      <c r="V147" s="4"/>
+      <c r="W147" s="4"/>
+      <c r="X147" s="4"/>
+      <c r="Y147" s="4"/>
+      <c r="Z147" s="4"/>
+    </row>
+    <row r="148" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A148" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B148" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
-      <c r="L148" s="6"/>
-      <c r="M148" s="6"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="6"/>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="6"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-      <c r="V148" s="6"/>
-      <c r="W148" s="6"/>
-      <c r="X148" s="6"/>
-      <c r="Y148" s="6"/>
-      <c r="Z148" s="6"/>
-    </row>
-    <row r="149" spans="1:26" ht="12.5">
-      <c r="A149" s="6" t="s">
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
+      <c r="L148" s="4"/>
+      <c r="M148" s="4"/>
+      <c r="N148" s="4"/>
+      <c r="O148" s="4"/>
+      <c r="P148" s="4"/>
+      <c r="Q148" s="4"/>
+      <c r="R148" s="4"/>
+      <c r="S148" s="4"/>
+      <c r="T148" s="4"/>
+      <c r="U148" s="4"/>
+      <c r="V148" s="4"/>
+      <c r="W148" s="4"/>
+      <c r="X148" s="4"/>
+      <c r="Y148" s="4"/>
+      <c r="Z148" s="4"/>
+    </row>
+    <row r="149" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A149" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B149" s="6" t="s">
+      <c r="B149" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
-      <c r="L149" s="6"/>
-      <c r="M149" s="6"/>
-      <c r="N149" s="6"/>
-      <c r="O149" s="6"/>
-      <c r="P149" s="6"/>
-      <c r="Q149" s="6"/>
-      <c r="R149" s="6"/>
-      <c r="S149" s="6"/>
-      <c r="T149" s="6"/>
-      <c r="U149" s="6"/>
-      <c r="V149" s="6"/>
-      <c r="W149" s="6"/>
-      <c r="X149" s="6"/>
-      <c r="Y149" s="6"/>
-      <c r="Z149" s="6"/>
-    </row>
-    <row r="150" spans="1:26" ht="12.5">
-      <c r="A150" s="6" t="s">
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
+      <c r="L149" s="4"/>
+      <c r="M149" s="4"/>
+      <c r="N149" s="4"/>
+      <c r="O149" s="4"/>
+      <c r="P149" s="4"/>
+      <c r="Q149" s="4"/>
+      <c r="R149" s="4"/>
+      <c r="S149" s="4"/>
+      <c r="T149" s="4"/>
+      <c r="U149" s="4"/>
+      <c r="V149" s="4"/>
+      <c r="W149" s="4"/>
+      <c r="X149" s="4"/>
+      <c r="Y149" s="4"/>
+      <c r="Z149" s="4"/>
+    </row>
+    <row r="150" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A150" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B150" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
-      <c r="L150" s="6"/>
-      <c r="M150" s="6"/>
-      <c r="N150" s="6"/>
-      <c r="O150" s="6"/>
-      <c r="P150" s="6"/>
-      <c r="Q150" s="6"/>
-      <c r="R150" s="6"/>
-      <c r="S150" s="6"/>
-      <c r="T150" s="6"/>
-      <c r="U150" s="6"/>
-      <c r="V150" s="6"/>
-      <c r="W150" s="6"/>
-      <c r="X150" s="6"/>
-      <c r="Y150" s="6"/>
-      <c r="Z150" s="6"/>
-    </row>
-    <row r="151" spans="1:26" ht="12.5">
-      <c r="A151" s="6" t="s">
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
+      <c r="K150" s="4"/>
+      <c r="L150" s="4"/>
+      <c r="M150" s="4"/>
+      <c r="N150" s="4"/>
+      <c r="O150" s="4"/>
+      <c r="P150" s="4"/>
+      <c r="Q150" s="4"/>
+      <c r="R150" s="4"/>
+      <c r="S150" s="4"/>
+      <c r="T150" s="4"/>
+      <c r="U150" s="4"/>
+      <c r="V150" s="4"/>
+      <c r="W150" s="4"/>
+      <c r="X150" s="4"/>
+      <c r="Y150" s="4"/>
+      <c r="Z150" s="4"/>
+    </row>
+    <row r="151" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A151" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B151" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
-      <c r="M151" s="6"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="6"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="6"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="6"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-    </row>
-    <row r="152" spans="1:26" ht="12.5">
-      <c r="A152" s="6" t="s">
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+      <c r="L151" s="4"/>
+      <c r="M151" s="4"/>
+      <c r="N151" s="4"/>
+      <c r="O151" s="4"/>
+      <c r="P151" s="4"/>
+      <c r="Q151" s="4"/>
+      <c r="R151" s="4"/>
+      <c r="S151" s="4"/>
+      <c r="T151" s="4"/>
+      <c r="U151" s="4"/>
+      <c r="V151" s="4"/>
+      <c r="W151" s="4"/>
+      <c r="X151" s="4"/>
+      <c r="Y151" s="4"/>
+      <c r="Z151" s="4"/>
+    </row>
+    <row r="152" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A152" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B152" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
-      <c r="L152" s="6"/>
-      <c r="M152" s="6"/>
-      <c r="N152" s="6"/>
-      <c r="O152" s="6"/>
-      <c r="P152" s="6"/>
-      <c r="Q152" s="6"/>
-      <c r="R152" s="6"/>
-      <c r="S152" s="6"/>
-      <c r="T152" s="6"/>
-      <c r="U152" s="6"/>
-      <c r="V152" s="6"/>
-      <c r="W152" s="6"/>
-      <c r="X152" s="6"/>
-      <c r="Y152" s="6"/>
-      <c r="Z152" s="6"/>
-    </row>
-    <row r="153" spans="1:26" ht="12.5">
-      <c r="A153" s="6" t="s">
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+      <c r="I152" s="4"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
+      <c r="L152" s="4"/>
+      <c r="M152" s="4"/>
+      <c r="N152" s="4"/>
+      <c r="O152" s="4"/>
+      <c r="P152" s="4"/>
+      <c r="Q152" s="4"/>
+      <c r="R152" s="4"/>
+      <c r="S152" s="4"/>
+      <c r="T152" s="4"/>
+      <c r="U152" s="4"/>
+      <c r="V152" s="4"/>
+      <c r="W152" s="4"/>
+      <c r="X152" s="4"/>
+      <c r="Y152" s="4"/>
+      <c r="Z152" s="4"/>
+    </row>
+    <row r="153" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A153" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B153" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
-      <c r="K153" s="6"/>
-      <c r="L153" s="6"/>
-      <c r="M153" s="6"/>
-      <c r="N153" s="6"/>
-      <c r="O153" s="6"/>
-      <c r="P153" s="6"/>
-      <c r="Q153" s="6"/>
-      <c r="R153" s="6"/>
-      <c r="S153" s="6"/>
-      <c r="T153" s="6"/>
-      <c r="U153" s="6"/>
-      <c r="V153" s="6"/>
-      <c r="W153" s="6"/>
-      <c r="X153" s="6"/>
-      <c r="Y153" s="6"/>
-      <c r="Z153" s="6"/>
-    </row>
-    <row r="154" spans="1:26" ht="12.5">
-      <c r="A154" s="6" t="s">
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4"/>
+      <c r="O153" s="4"/>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="4"/>
+      <c r="R153" s="4"/>
+      <c r="S153" s="4"/>
+      <c r="T153" s="4"/>
+      <c r="U153" s="4"/>
+      <c r="V153" s="4"/>
+      <c r="W153" s="4"/>
+      <c r="X153" s="4"/>
+      <c r="Y153" s="4"/>
+      <c r="Z153" s="4"/>
+    </row>
+    <row r="154" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A154" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B154" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
-      <c r="L154" s="6"/>
-      <c r="M154" s="6"/>
-      <c r="N154" s="6"/>
-      <c r="O154" s="6"/>
-      <c r="P154" s="6"/>
-      <c r="Q154" s="6"/>
-      <c r="R154" s="6"/>
-      <c r="S154" s="6"/>
-      <c r="T154" s="6"/>
-      <c r="U154" s="6"/>
-      <c r="V154" s="6"/>
-      <c r="W154" s="6"/>
-      <c r="X154" s="6"/>
-      <c r="Y154" s="6"/>
-      <c r="Z154" s="6"/>
-    </row>
-    <row r="155" spans="1:26" ht="12.5">
-      <c r="A155" s="6" t="s">
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+      <c r="L154" s="4"/>
+      <c r="M154" s="4"/>
+      <c r="N154" s="4"/>
+      <c r="O154" s="4"/>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="4"/>
+      <c r="R154" s="4"/>
+      <c r="S154" s="4"/>
+      <c r="T154" s="4"/>
+      <c r="U154" s="4"/>
+      <c r="V154" s="4"/>
+      <c r="W154" s="4"/>
+      <c r="X154" s="4"/>
+      <c r="Y154" s="4"/>
+      <c r="Z154" s="4"/>
+    </row>
+    <row r="155" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A155" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B155" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
-      <c r="L155" s="6"/>
-      <c r="M155" s="6"/>
-      <c r="N155" s="6"/>
-      <c r="O155" s="6"/>
-      <c r="P155" s="6"/>
-      <c r="Q155" s="6"/>
-      <c r="R155" s="6"/>
-      <c r="S155" s="6"/>
-      <c r="T155" s="6"/>
-      <c r="U155" s="6"/>
-      <c r="V155" s="6"/>
-      <c r="W155" s="6"/>
-      <c r="X155" s="6"/>
-      <c r="Y155" s="6"/>
-      <c r="Z155" s="6"/>
-    </row>
-    <row r="156" spans="1:26" ht="12.5">
-      <c r="A156" s="6" t="s">
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
+      <c r="L155" s="4"/>
+      <c r="M155" s="4"/>
+      <c r="N155" s="4"/>
+      <c r="O155" s="4"/>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="4"/>
+      <c r="R155" s="4"/>
+      <c r="S155" s="4"/>
+      <c r="T155" s="4"/>
+      <c r="U155" s="4"/>
+      <c r="V155" s="4"/>
+      <c r="W155" s="4"/>
+      <c r="X155" s="4"/>
+      <c r="Y155" s="4"/>
+      <c r="Z155" s="4"/>
+    </row>
+    <row r="156" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A156" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B156" s="6" t="s">
+      <c r="B156" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
-      <c r="M156" s="6"/>
-      <c r="N156" s="6"/>
-      <c r="O156" s="6"/>
-      <c r="P156" s="6"/>
-      <c r="Q156" s="6"/>
-      <c r="R156" s="6"/>
-      <c r="S156" s="6"/>
-      <c r="T156" s="6"/>
-      <c r="U156" s="6"/>
-      <c r="V156" s="6"/>
-      <c r="W156" s="6"/>
-      <c r="X156" s="6"/>
-      <c r="Y156" s="6"/>
-      <c r="Z156" s="6"/>
-    </row>
-    <row r="157" spans="1:26" ht="12.5">
-      <c r="A157" s="6" t="s">
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4"/>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4"/>
+      <c r="I156" s="4"/>
+      <c r="J156" s="4"/>
+      <c r="K156" s="4"/>
+      <c r="L156" s="4"/>
+      <c r="M156" s="4"/>
+      <c r="N156" s="4"/>
+      <c r="O156" s="4"/>
+      <c r="P156" s="4"/>
+      <c r="Q156" s="4"/>
+      <c r="R156" s="4"/>
+      <c r="S156" s="4"/>
+      <c r="T156" s="4"/>
+      <c r="U156" s="4"/>
+      <c r="V156" s="4"/>
+      <c r="W156" s="4"/>
+      <c r="X156" s="4"/>
+      <c r="Y156" s="4"/>
+      <c r="Z156" s="4"/>
+    </row>
+    <row r="157" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A157" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B157" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6"/>
-      <c r="L157" s="6"/>
-      <c r="M157" s="6"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="6"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="6"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="6"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-    </row>
-    <row r="158" spans="1:26" ht="12.5">
-      <c r="A158" s="6" t="s">
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
+      <c r="I157" s="4"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
+      <c r="L157" s="4"/>
+      <c r="M157" s="4"/>
+      <c r="N157" s="4"/>
+      <c r="O157" s="4"/>
+      <c r="P157" s="4"/>
+      <c r="Q157" s="4"/>
+      <c r="R157" s="4"/>
+      <c r="S157" s="4"/>
+      <c r="T157" s="4"/>
+      <c r="U157" s="4"/>
+      <c r="V157" s="4"/>
+      <c r="W157" s="4"/>
+      <c r="X157" s="4"/>
+      <c r="Y157" s="4"/>
+      <c r="Z157" s="4"/>
+    </row>
+    <row r="158" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A158" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B158" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
-      <c r="L158" s="6"/>
-      <c r="M158" s="6"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="6"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="6"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="6"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-    </row>
-    <row r="159" spans="1:26" ht="12.5">
-      <c r="A159" s="6" t="s">
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4"/>
+      <c r="G158" s="4"/>
+      <c r="H158" s="4"/>
+      <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="4"/>
+      <c r="L158" s="4"/>
+      <c r="M158" s="4"/>
+      <c r="N158" s="4"/>
+      <c r="O158" s="4"/>
+      <c r="P158" s="4"/>
+      <c r="Q158" s="4"/>
+      <c r="R158" s="4"/>
+      <c r="S158" s="4"/>
+      <c r="T158" s="4"/>
+      <c r="U158" s="4"/>
+      <c r="V158" s="4"/>
+      <c r="W158" s="4"/>
+      <c r="X158" s="4"/>
+      <c r="Y158" s="4"/>
+      <c r="Z158" s="4"/>
+    </row>
+    <row r="159" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A159" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B159" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
-      <c r="L159" s="6"/>
-      <c r="M159" s="6"/>
-      <c r="N159" s="6"/>
-      <c r="O159" s="6"/>
-      <c r="P159" s="6"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="6"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="6"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-    </row>
-    <row r="160" spans="1:26" ht="12.5">
-      <c r="A160" s="6" t="s">
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+      <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+      <c r="L159" s="4"/>
+      <c r="M159" s="4"/>
+      <c r="N159" s="4"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="4"/>
+      <c r="R159" s="4"/>
+      <c r="S159" s="4"/>
+      <c r="T159" s="4"/>
+      <c r="U159" s="4"/>
+      <c r="V159" s="4"/>
+      <c r="W159" s="4"/>
+      <c r="X159" s="4"/>
+      <c r="Y159" s="4"/>
+      <c r="Z159" s="4"/>
+    </row>
+    <row r="160" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A160" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B160" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="6"/>
-      <c r="K160" s="6"/>
-      <c r="L160" s="6"/>
-      <c r="M160" s="6"/>
-      <c r="N160" s="6"/>
-      <c r="O160" s="6"/>
-      <c r="P160" s="6"/>
-      <c r="Q160" s="6"/>
-      <c r="R160" s="6"/>
-      <c r="S160" s="6"/>
-      <c r="T160" s="6"/>
-      <c r="U160" s="6"/>
-      <c r="V160" s="6"/>
-      <c r="W160" s="6"/>
-      <c r="X160" s="6"/>
-      <c r="Y160" s="6"/>
-      <c r="Z160" s="6"/>
-    </row>
-    <row r="161" spans="1:26" ht="12.5">
-      <c r="A161" s="1" t="s">
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+      <c r="I160" s="4"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="4"/>
+      <c r="L160" s="4"/>
+      <c r="M160" s="4"/>
+      <c r="N160" s="4"/>
+      <c r="O160" s="4"/>
+      <c r="P160" s="4"/>
+      <c r="Q160" s="4"/>
+      <c r="R160" s="4"/>
+      <c r="S160" s="4"/>
+      <c r="T160" s="4"/>
+      <c r="U160" s="4"/>
+      <c r="V160" s="4"/>
+      <c r="W160" s="4"/>
+      <c r="X160" s="4"/>
+      <c r="Y160" s="4"/>
+      <c r="Z160" s="4"/>
+    </row>
+    <row r="161" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A161" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B161" s="10" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="162" spans="1:26" ht="12.5">
-      <c r="A162" s="1" t="s">
+    <row r="162" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A162" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B162" s="10" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="163" spans="1:26" ht="12.5">
-      <c r="A163" s="1" t="s">
+    <row r="163" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A163" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="164" spans="1:26" ht="12.5">
-      <c r="A164" s="9" t="s">
+    <row r="164" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A164" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" s="10" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="165" spans="1:26" ht="12.5">
-      <c r="A165" s="9" t="s">
+    <row r="165" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A165" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B165" s="10" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="166" spans="1:26" ht="12.5">
-      <c r="A166" s="9" t="s">
+    <row r="166" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A166" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B166" s="10" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="167" spans="1:26" ht="12.5">
-      <c r="A167" s="10" t="s">
+    <row r="167" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A167" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B167" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
-      <c r="L167" s="6"/>
-      <c r="M167" s="6"/>
-      <c r="N167" s="6"/>
-      <c r="O167" s="6"/>
-      <c r="P167" s="6"/>
-      <c r="Q167" s="6"/>
-      <c r="R167" s="6"/>
-      <c r="S167" s="6"/>
-      <c r="T167" s="6"/>
-      <c r="U167" s="6"/>
-      <c r="V167" s="6"/>
-      <c r="W167" s="6"/>
-      <c r="X167" s="6"/>
-      <c r="Y167" s="6"/>
-      <c r="Z167" s="6"/>
-    </row>
-    <row r="168" spans="1:26" ht="12.5">
-      <c r="A168" s="10" t="s">
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
+      <c r="I167" s="4"/>
+      <c r="J167" s="4"/>
+      <c r="K167" s="4"/>
+      <c r="L167" s="4"/>
+      <c r="M167" s="4"/>
+      <c r="N167" s="4"/>
+      <c r="O167" s="4"/>
+      <c r="P167" s="4"/>
+      <c r="Q167" s="4"/>
+      <c r="R167" s="4"/>
+      <c r="S167" s="4"/>
+      <c r="T167" s="4"/>
+      <c r="U167" s="4"/>
+      <c r="V167" s="4"/>
+      <c r="W167" s="4"/>
+      <c r="X167" s="4"/>
+      <c r="Y167" s="4"/>
+      <c r="Z167" s="4"/>
+    </row>
+    <row r="168" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A168" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B168" s="6" t="s">
+      <c r="B168" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
-      <c r="L168" s="6"/>
-      <c r="M168" s="6"/>
-      <c r="N168" s="6"/>
-      <c r="O168" s="6"/>
-      <c r="P168" s="6"/>
-      <c r="Q168" s="6"/>
-      <c r="R168" s="6"/>
-      <c r="S168" s="6"/>
-      <c r="T168" s="6"/>
-      <c r="U168" s="6"/>
-      <c r="V168" s="6"/>
-      <c r="W168" s="6"/>
-      <c r="X168" s="6"/>
-      <c r="Y168" s="6"/>
-      <c r="Z168" s="6"/>
-    </row>
-    <row r="169" spans="1:26" ht="12.5">
-      <c r="A169" s="10" t="s">
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
+      <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="4"/>
+      <c r="L168" s="4"/>
+      <c r="M168" s="4"/>
+      <c r="N168" s="4"/>
+      <c r="O168" s="4"/>
+      <c r="P168" s="4"/>
+      <c r="Q168" s="4"/>
+      <c r="R168" s="4"/>
+      <c r="S168" s="4"/>
+      <c r="T168" s="4"/>
+      <c r="U168" s="4"/>
+      <c r="V168" s="4"/>
+      <c r="W168" s="4"/>
+      <c r="X168" s="4"/>
+      <c r="Y168" s="4"/>
+      <c r="Z168" s="4"/>
+    </row>
+    <row r="169" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A169" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B169" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
-      <c r="L169" s="6"/>
-      <c r="M169" s="6"/>
-      <c r="N169" s="6"/>
-      <c r="O169" s="6"/>
-      <c r="P169" s="6"/>
-      <c r="Q169" s="6"/>
-      <c r="R169" s="6"/>
-      <c r="S169" s="6"/>
-      <c r="T169" s="6"/>
-      <c r="U169" s="6"/>
-      <c r="V169" s="6"/>
-      <c r="W169" s="6"/>
-      <c r="X169" s="6"/>
-      <c r="Y169" s="6"/>
-      <c r="Z169" s="6"/>
-    </row>
-    <row r="170" spans="1:26" ht="12.5">
-      <c r="A170" s="10" t="s">
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+      <c r="I169" s="4"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
+      <c r="L169" s="4"/>
+      <c r="M169" s="4"/>
+      <c r="N169" s="4"/>
+      <c r="O169" s="4"/>
+      <c r="P169" s="4"/>
+      <c r="Q169" s="4"/>
+      <c r="R169" s="4"/>
+      <c r="S169" s="4"/>
+      <c r="T169" s="4"/>
+      <c r="U169" s="4"/>
+      <c r="V169" s="4"/>
+      <c r="W169" s="4"/>
+      <c r="X169" s="4"/>
+      <c r="Y169" s="4"/>
+      <c r="Z169" s="4"/>
+    </row>
+    <row r="170" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A170" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B170" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
-      <c r="L170" s="6"/>
-      <c r="M170" s="6"/>
-      <c r="N170" s="6"/>
-      <c r="O170" s="6"/>
-      <c r="P170" s="6"/>
-      <c r="Q170" s="6"/>
-      <c r="R170" s="6"/>
-      <c r="S170" s="6"/>
-      <c r="T170" s="6"/>
-      <c r="U170" s="6"/>
-      <c r="V170" s="6"/>
-      <c r="W170" s="6"/>
-      <c r="X170" s="6"/>
-      <c r="Y170" s="6"/>
-      <c r="Z170" s="6"/>
-    </row>
-    <row r="171" spans="1:26" ht="12.5">
-      <c r="A171" s="10" t="s">
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
+      <c r="G170" s="4"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="4"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="4"/>
+      <c r="L170" s="4"/>
+      <c r="M170" s="4"/>
+      <c r="N170" s="4"/>
+      <c r="O170" s="4"/>
+      <c r="P170" s="4"/>
+      <c r="Q170" s="4"/>
+      <c r="R170" s="4"/>
+      <c r="S170" s="4"/>
+      <c r="T170" s="4"/>
+      <c r="U170" s="4"/>
+      <c r="V170" s="4"/>
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+      <c r="Z170" s="4"/>
+    </row>
+    <row r="171" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A171" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B171" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
-      <c r="M171" s="6"/>
-      <c r="N171" s="6"/>
-      <c r="O171" s="6"/>
-      <c r="P171" s="6"/>
-      <c r="Q171" s="6"/>
-      <c r="R171" s="6"/>
-      <c r="S171" s="6"/>
-      <c r="T171" s="6"/>
-      <c r="U171" s="6"/>
-      <c r="V171" s="6"/>
-      <c r="W171" s="6"/>
-      <c r="X171" s="6"/>
-      <c r="Y171" s="6"/>
-      <c r="Z171" s="6"/>
-    </row>
-    <row r="172" spans="1:26" ht="12.5">
-      <c r="A172" s="12" t="s">
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+      <c r="L171" s="4"/>
+      <c r="M171" s="4"/>
+      <c r="N171" s="4"/>
+      <c r="O171" s="4"/>
+      <c r="P171" s="4"/>
+      <c r="Q171" s="4"/>
+      <c r="R171" s="4"/>
+      <c r="S171" s="4"/>
+      <c r="T171" s="4"/>
+      <c r="U171" s="4"/>
+      <c r="V171" s="4"/>
+      <c r="W171" s="4"/>
+      <c r="X171" s="4"/>
+      <c r="Y171" s="4"/>
+      <c r="Z171" s="4"/>
+    </row>
+    <row r="172" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A172" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
-      <c r="L172" s="6"/>
-      <c r="M172" s="6"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="6"/>
-      <c r="Q172" s="6"/>
-      <c r="R172" s="6"/>
-      <c r="S172" s="6"/>
-      <c r="T172" s="6"/>
-      <c r="U172" s="6"/>
-      <c r="V172" s="6"/>
-      <c r="W172" s="6"/>
-      <c r="X172" s="6"/>
-      <c r="Y172" s="6"/>
-      <c r="Z172" s="6"/>
-    </row>
-    <row r="173" spans="1:26" ht="12.5">
-      <c r="A173" s="12" t="s">
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
+      <c r="G172" s="4"/>
+      <c r="H172" s="4"/>
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
+      <c r="L172" s="4"/>
+      <c r="M172" s="4"/>
+      <c r="N172" s="4"/>
+      <c r="O172" s="4"/>
+      <c r="P172" s="4"/>
+      <c r="Q172" s="4"/>
+      <c r="R172" s="4"/>
+      <c r="S172" s="4"/>
+      <c r="T172" s="4"/>
+      <c r="U172" s="4"/>
+      <c r="V172" s="4"/>
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+      <c r="Z172" s="4"/>
+    </row>
+    <row r="173" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A173" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B173" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
-      <c r="L173" s="6"/>
-      <c r="M173" s="6"/>
-      <c r="N173" s="6"/>
-      <c r="O173" s="6"/>
-      <c r="P173" s="6"/>
-      <c r="Q173" s="6"/>
-      <c r="R173" s="6"/>
-      <c r="S173" s="6"/>
-      <c r="T173" s="6"/>
-      <c r="U173" s="6"/>
-      <c r="V173" s="6"/>
-      <c r="W173" s="6"/>
-      <c r="X173" s="6"/>
-      <c r="Y173" s="6"/>
-      <c r="Z173" s="6"/>
-    </row>
-    <row r="174" spans="1:26" ht="12.5">
-      <c r="A174" s="12" t="s">
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+      <c r="I173" s="4"/>
+      <c r="J173" s="4"/>
+      <c r="K173" s="4"/>
+      <c r="L173" s="4"/>
+      <c r="M173" s="4"/>
+      <c r="N173" s="4"/>
+      <c r="O173" s="4"/>
+      <c r="P173" s="4"/>
+      <c r="Q173" s="4"/>
+      <c r="R173" s="4"/>
+      <c r="S173" s="4"/>
+      <c r="T173" s="4"/>
+      <c r="U173" s="4"/>
+      <c r="V173" s="4"/>
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+      <c r="Z173" s="4"/>
+    </row>
+    <row r="174" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A174" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B174" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
-      <c r="L174" s="6"/>
-      <c r="M174" s="6"/>
-      <c r="N174" s="6"/>
-      <c r="O174" s="6"/>
-      <c r="P174" s="6"/>
-      <c r="Q174" s="6"/>
-      <c r="R174" s="6"/>
-      <c r="S174" s="6"/>
-      <c r="T174" s="6"/>
-      <c r="U174" s="6"/>
-      <c r="V174" s="6"/>
-      <c r="W174" s="6"/>
-      <c r="X174" s="6"/>
-      <c r="Y174" s="6"/>
-      <c r="Z174" s="6"/>
-    </row>
-    <row r="175" spans="1:26" ht="12.5">
-      <c r="A175" s="12" t="s">
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4"/>
+      <c r="G174" s="4"/>
+      <c r="H174" s="4"/>
+      <c r="I174" s="4"/>
+      <c r="J174" s="4"/>
+      <c r="K174" s="4"/>
+      <c r="L174" s="4"/>
+      <c r="M174" s="4"/>
+      <c r="N174" s="4"/>
+      <c r="O174" s="4"/>
+      <c r="P174" s="4"/>
+      <c r="Q174" s="4"/>
+      <c r="R174" s="4"/>
+      <c r="S174" s="4"/>
+      <c r="T174" s="4"/>
+      <c r="U174" s="4"/>
+      <c r="V174" s="4"/>
+      <c r="W174" s="4"/>
+      <c r="X174" s="4"/>
+      <c r="Y174" s="4"/>
+      <c r="Z174" s="4"/>
+    </row>
+    <row r="175" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A175" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B175" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
-      <c r="M175" s="6"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="6"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="6"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="6"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-    </row>
-    <row r="176" spans="1:26" ht="12.5">
-      <c r="A176" s="12" t="s">
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
+      <c r="G175" s="4"/>
+      <c r="H175" s="4"/>
+      <c r="I175" s="4"/>
+      <c r="J175" s="4"/>
+      <c r="K175" s="4"/>
+      <c r="L175" s="4"/>
+      <c r="M175" s="4"/>
+      <c r="N175" s="4"/>
+      <c r="O175" s="4"/>
+      <c r="P175" s="4"/>
+      <c r="Q175" s="4"/>
+      <c r="R175" s="4"/>
+      <c r="S175" s="4"/>
+      <c r="T175" s="4"/>
+      <c r="U175" s="4"/>
+      <c r="V175" s="4"/>
+      <c r="W175" s="4"/>
+      <c r="X175" s="4"/>
+      <c r="Y175" s="4"/>
+      <c r="Z175" s="4"/>
+    </row>
+    <row r="176" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A176" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B176" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
-      <c r="M176" s="6"/>
-      <c r="N176" s="6"/>
-      <c r="O176" s="6"/>
-      <c r="P176" s="6"/>
-      <c r="Q176" s="6"/>
-      <c r="R176" s="6"/>
-      <c r="S176" s="6"/>
-      <c r="T176" s="6"/>
-      <c r="U176" s="6"/>
-      <c r="V176" s="6"/>
-      <c r="W176" s="6"/>
-      <c r="X176" s="6"/>
-      <c r="Y176" s="6"/>
-      <c r="Z176" s="6"/>
-    </row>
-    <row r="177" spans="1:26" ht="12.5">
-      <c r="A177" s="12" t="s">
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
+      <c r="G176" s="4"/>
+      <c r="H176" s="4"/>
+      <c r="I176" s="4"/>
+      <c r="J176" s="4"/>
+      <c r="K176" s="4"/>
+      <c r="L176" s="4"/>
+      <c r="M176" s="4"/>
+      <c r="N176" s="4"/>
+      <c r="O176" s="4"/>
+      <c r="P176" s="4"/>
+      <c r="Q176" s="4"/>
+      <c r="R176" s="4"/>
+      <c r="S176" s="4"/>
+      <c r="T176" s="4"/>
+      <c r="U176" s="4"/>
+      <c r="V176" s="4"/>
+      <c r="W176" s="4"/>
+      <c r="X176" s="4"/>
+      <c r="Y176" s="4"/>
+      <c r="Z176" s="4"/>
+    </row>
+    <row r="177" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A177" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B177" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
-      <c r="K177" s="6"/>
-      <c r="L177" s="6"/>
-      <c r="M177" s="6"/>
-      <c r="N177" s="6"/>
-      <c r="O177" s="6"/>
-      <c r="P177" s="6"/>
-      <c r="Q177" s="6"/>
-      <c r="R177" s="6"/>
-      <c r="S177" s="6"/>
-      <c r="T177" s="6"/>
-      <c r="U177" s="6"/>
-      <c r="V177" s="6"/>
-      <c r="W177" s="6"/>
-      <c r="X177" s="6"/>
-      <c r="Y177" s="6"/>
-      <c r="Z177" s="6"/>
-    </row>
-    <row r="178" spans="1:26" ht="12.5">
-      <c r="A178" s="9" t="s">
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
+      <c r="I177" s="4"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
+      <c r="L177" s="4"/>
+      <c r="M177" s="4"/>
+      <c r="N177" s="4"/>
+      <c r="O177" s="4"/>
+      <c r="P177" s="4"/>
+      <c r="Q177" s="4"/>
+      <c r="R177" s="4"/>
+      <c r="S177" s="4"/>
+      <c r="T177" s="4"/>
+      <c r="U177" s="4"/>
+      <c r="V177" s="4"/>
+      <c r="W177" s="4"/>
+      <c r="X177" s="4"/>
+      <c r="Y177" s="4"/>
+      <c r="Z177" s="4"/>
+    </row>
+    <row r="178" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A178" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="B178" s="14" t="s">
+      <c r="B178" s="18" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="179" spans="1:26" ht="12.5">
-      <c r="A179" s="9" t="s">
+    <row r="179" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A179" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="B179" s="14" t="s">
+      <c r="B179" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="180" spans="1:26" ht="12.5">
-      <c r="A180" s="11" t="s">
+    <row r="180" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A180" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B180" s="10" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="181" spans="1:26" ht="12.5">
-      <c r="A181" s="11" t="s">
+    <row r="181" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A181" s="17" t="s">
         <v>327</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B181" s="10" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="182" spans="1:26" ht="12.5">
-      <c r="A182" s="11" t="s">
+    <row r="182" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A182" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B182" s="10" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="183" spans="1:26" ht="12.5">
-      <c r="A183" s="11" t="s">
+    <row r="183" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A183" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B183" s="10" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:26" ht="12.5">
-      <c r="A184" s="11" t="s">
+    <row r="184" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A184" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B184" s="10" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="185" spans="1:26" ht="12.5">
-      <c r="A185" s="11" t="s">
+    <row r="185" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A185" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B185" s="10" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="186" spans="1:26" ht="12.5">
-      <c r="A186" s="9" t="s">
+    <row r="186" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A186" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="B186" s="10" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="187" spans="1:26" ht="12.5">
-      <c r="A187" s="9" t="s">
+    <row r="187" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A187" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="B187" s="15" t="s">
+      <c r="B187" s="19" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="188" spans="1:26" ht="12.5">
-      <c r="A188" s="9" t="s">
+    <row r="188" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A188" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B188" s="14" t="s">
+      <c r="B188" s="18" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="189" spans="1:26" ht="12.5">
-      <c r="A189" s="12" t="s">
+    <row r="189" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A189" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B189" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6"/>
-      <c r="M189" s="6"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="6"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="6"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="6"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-    </row>
-    <row r="190" spans="1:26" ht="12.5">
-      <c r="A190" s="12" t="s">
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+      <c r="L189" s="4"/>
+      <c r="M189" s="4"/>
+      <c r="N189" s="4"/>
+      <c r="O189" s="4"/>
+      <c r="P189" s="4"/>
+      <c r="Q189" s="4"/>
+      <c r="R189" s="4"/>
+      <c r="S189" s="4"/>
+      <c r="T189" s="4"/>
+      <c r="U189" s="4"/>
+      <c r="V189" s="4"/>
+      <c r="W189" s="4"/>
+      <c r="X189" s="4"/>
+      <c r="Y189" s="4"/>
+      <c r="Z189" s="4"/>
+    </row>
+    <row r="190" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A190" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B190" s="6" t="s">
+      <c r="B190" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
-      <c r="L190" s="6"/>
-      <c r="M190" s="6"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="6"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="6"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="6"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-    </row>
-    <row r="191" spans="1:26" ht="12.5">
-      <c r="A191" s="12" t="s">
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
+      <c r="I190" s="4"/>
+      <c r="J190" s="4"/>
+      <c r="K190" s="4"/>
+      <c r="L190" s="4"/>
+      <c r="M190" s="4"/>
+      <c r="N190" s="4"/>
+      <c r="O190" s="4"/>
+      <c r="P190" s="4"/>
+      <c r="Q190" s="4"/>
+      <c r="R190" s="4"/>
+      <c r="S190" s="4"/>
+      <c r="T190" s="4"/>
+      <c r="U190" s="4"/>
+      <c r="V190" s="4"/>
+      <c r="W190" s="4"/>
+      <c r="X190" s="4"/>
+      <c r="Y190" s="4"/>
+      <c r="Z190" s="4"/>
+    </row>
+    <row r="191" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A191" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B191" s="16" t="s">
+      <c r="B191" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
-      <c r="L191" s="6"/>
-      <c r="M191" s="6"/>
-      <c r="N191" s="6"/>
-      <c r="O191" s="6"/>
-      <c r="P191" s="6"/>
-      <c r="Q191" s="6"/>
-      <c r="R191" s="6"/>
-      <c r="S191" s="6"/>
-      <c r="T191" s="6"/>
-      <c r="U191" s="6"/>
-      <c r="V191" s="6"/>
-      <c r="W191" s="6"/>
-      <c r="X191" s="6"/>
-      <c r="Y191" s="6"/>
-      <c r="Z191" s="6"/>
-    </row>
-    <row r="192" spans="1:26" ht="12.5">
-      <c r="A192" s="12" t="s">
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
+      <c r="I191" s="4"/>
+      <c r="J191" s="4"/>
+      <c r="K191" s="4"/>
+      <c r="L191" s="4"/>
+      <c r="M191" s="4"/>
+      <c r="N191" s="4"/>
+      <c r="O191" s="4"/>
+      <c r="P191" s="4"/>
+      <c r="Q191" s="4"/>
+      <c r="R191" s="4"/>
+      <c r="S191" s="4"/>
+      <c r="T191" s="4"/>
+      <c r="U191" s="4"/>
+      <c r="V191" s="4"/>
+      <c r="W191" s="4"/>
+      <c r="X191" s="4"/>
+      <c r="Y191" s="4"/>
+      <c r="Z191" s="4"/>
+    </row>
+    <row r="192" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A192" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B192" s="6" t="s">
+      <c r="B192" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
-      <c r="L192" s="6"/>
-      <c r="M192" s="6"/>
-      <c r="N192" s="6"/>
-      <c r="O192" s="6"/>
-      <c r="P192" s="6"/>
-      <c r="Q192" s="6"/>
-      <c r="R192" s="6"/>
-      <c r="S192" s="6"/>
-      <c r="T192" s="6"/>
-      <c r="U192" s="6"/>
-      <c r="V192" s="6"/>
-      <c r="W192" s="6"/>
-      <c r="X192" s="6"/>
-      <c r="Y192" s="6"/>
-      <c r="Z192" s="6"/>
-    </row>
-    <row r="193" spans="1:26" ht="12.5">
-      <c r="A193" s="12" t="s">
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
+      <c r="I192" s="4"/>
+      <c r="J192" s="4"/>
+      <c r="K192" s="4"/>
+      <c r="L192" s="4"/>
+      <c r="M192" s="4"/>
+      <c r="N192" s="4"/>
+      <c r="O192" s="4"/>
+      <c r="P192" s="4"/>
+      <c r="Q192" s="4"/>
+      <c r="R192" s="4"/>
+      <c r="S192" s="4"/>
+      <c r="T192" s="4"/>
+      <c r="U192" s="4"/>
+      <c r="V192" s="4"/>
+      <c r="W192" s="4"/>
+      <c r="X192" s="4"/>
+      <c r="Y192" s="4"/>
+      <c r="Z192" s="4"/>
+    </row>
+    <row r="193" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A193" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B193" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="6"/>
-      <c r="L193" s="6"/>
-      <c r="M193" s="6"/>
-      <c r="N193" s="6"/>
-      <c r="O193" s="6"/>
-      <c r="P193" s="6"/>
-      <c r="Q193" s="6"/>
-      <c r="R193" s="6"/>
-      <c r="S193" s="6"/>
-      <c r="T193" s="6"/>
-      <c r="U193" s="6"/>
-      <c r="V193" s="6"/>
-      <c r="W193" s="6"/>
-      <c r="X193" s="6"/>
-      <c r="Y193" s="6"/>
-      <c r="Z193" s="6"/>
-    </row>
-    <row r="194" spans="1:26" ht="12.5">
-      <c r="A194" s="12" t="s">
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+      <c r="I193" s="4"/>
+      <c r="J193" s="4"/>
+      <c r="K193" s="4"/>
+      <c r="L193" s="4"/>
+      <c r="M193" s="4"/>
+      <c r="N193" s="4"/>
+      <c r="O193" s="4"/>
+      <c r="P193" s="4"/>
+      <c r="Q193" s="4"/>
+      <c r="R193" s="4"/>
+      <c r="S193" s="4"/>
+      <c r="T193" s="4"/>
+      <c r="U193" s="4"/>
+      <c r="V193" s="4"/>
+      <c r="W193" s="4"/>
+      <c r="X193" s="4"/>
+      <c r="Y193" s="4"/>
+      <c r="Z193" s="4"/>
+    </row>
+    <row r="194" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A194" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B194" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
-      <c r="L194" s="6"/>
-      <c r="M194" s="6"/>
-      <c r="N194" s="6"/>
-      <c r="O194" s="6"/>
-      <c r="P194" s="6"/>
-      <c r="Q194" s="6"/>
-      <c r="R194" s="6"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
-      <c r="X194" s="6"/>
-      <c r="Y194" s="6"/>
-      <c r="Z194" s="6"/>
-    </row>
-    <row r="195" spans="1:26" ht="12.5">
-      <c r="A195" s="12" t="s">
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
+      <c r="G194" s="4"/>
+      <c r="H194" s="4"/>
+      <c r="I194" s="4"/>
+      <c r="J194" s="4"/>
+      <c r="K194" s="4"/>
+      <c r="L194" s="4"/>
+      <c r="M194" s="4"/>
+      <c r="N194" s="4"/>
+      <c r="O194" s="4"/>
+      <c r="P194" s="4"/>
+      <c r="Q194" s="4"/>
+      <c r="R194" s="4"/>
+      <c r="S194" s="4"/>
+      <c r="T194" s="4"/>
+      <c r="U194" s="4"/>
+      <c r="V194" s="4"/>
+      <c r="W194" s="4"/>
+      <c r="X194" s="4"/>
+      <c r="Y194" s="4"/>
+      <c r="Z194" s="4"/>
+    </row>
+    <row r="195" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A195" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B195" s="16" t="s">
+      <c r="B195" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="6"/>
-      <c r="L195" s="6"/>
-      <c r="M195" s="6"/>
-      <c r="N195" s="6"/>
-      <c r="O195" s="6"/>
-      <c r="P195" s="6"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="6"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="6"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-    </row>
-    <row r="196" spans="1:26" ht="12.5">
-      <c r="A196" s="12" t="s">
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
+      <c r="I195" s="4"/>
+      <c r="J195" s="4"/>
+      <c r="K195" s="4"/>
+      <c r="L195" s="4"/>
+      <c r="M195" s="4"/>
+      <c r="N195" s="4"/>
+      <c r="O195" s="4"/>
+      <c r="P195" s="4"/>
+      <c r="Q195" s="4"/>
+      <c r="R195" s="4"/>
+      <c r="S195" s="4"/>
+      <c r="T195" s="4"/>
+      <c r="U195" s="4"/>
+      <c r="V195" s="4"/>
+      <c r="W195" s="4"/>
+      <c r="X195" s="4"/>
+      <c r="Y195" s="4"/>
+      <c r="Z195" s="4"/>
+    </row>
+    <row r="196" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A196" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="B196" s="6" t="s">
+      <c r="B196" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
-      <c r="L196" s="6"/>
-      <c r="M196" s="6"/>
-      <c r="N196" s="6"/>
-      <c r="O196" s="6"/>
-      <c r="P196" s="6"/>
-      <c r="Q196" s="6"/>
-      <c r="R196" s="6"/>
-      <c r="S196" s="6"/>
-      <c r="T196" s="6"/>
-      <c r="U196" s="6"/>
-      <c r="V196" s="6"/>
-      <c r="W196" s="6"/>
-      <c r="X196" s="6"/>
-      <c r="Y196" s="6"/>
-      <c r="Z196" s="6"/>
-    </row>
-    <row r="197" spans="1:26" ht="12.5">
-      <c r="A197" s="10" t="s">
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+      <c r="G196" s="4"/>
+      <c r="H196" s="4"/>
+      <c r="I196" s="4"/>
+      <c r="J196" s="4"/>
+      <c r="K196" s="4"/>
+      <c r="L196" s="4"/>
+      <c r="M196" s="4"/>
+      <c r="N196" s="4"/>
+      <c r="O196" s="4"/>
+      <c r="P196" s="4"/>
+      <c r="Q196" s="4"/>
+      <c r="R196" s="4"/>
+      <c r="S196" s="4"/>
+      <c r="T196" s="4"/>
+      <c r="U196" s="4"/>
+      <c r="V196" s="4"/>
+      <c r="W196" s="4"/>
+      <c r="X196" s="4"/>
+      <c r="Y196" s="4"/>
+      <c r="Z196" s="4"/>
+    </row>
+    <row r="197" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A197" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="B197" s="6" t="s">
+      <c r="B197" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
-      <c r="M197" s="6"/>
-      <c r="N197" s="6"/>
-      <c r="O197" s="6"/>
-      <c r="P197" s="6"/>
-      <c r="Q197" s="6"/>
-      <c r="R197" s="6"/>
-      <c r="S197" s="6"/>
-      <c r="T197" s="6"/>
-      <c r="U197" s="6"/>
-      <c r="V197" s="6"/>
-      <c r="W197" s="6"/>
-      <c r="X197" s="6"/>
-      <c r="Y197" s="6"/>
-      <c r="Z197" s="6"/>
-    </row>
-    <row r="198" spans="1:26" ht="12.5">
-      <c r="A198" s="10" t="s">
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
+      <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
+      <c r="K197" s="4"/>
+      <c r="L197" s="4"/>
+      <c r="M197" s="4"/>
+      <c r="N197" s="4"/>
+      <c r="O197" s="4"/>
+      <c r="P197" s="4"/>
+      <c r="Q197" s="4"/>
+      <c r="R197" s="4"/>
+      <c r="S197" s="4"/>
+      <c r="T197" s="4"/>
+      <c r="U197" s="4"/>
+      <c r="V197" s="4"/>
+      <c r="W197" s="4"/>
+      <c r="X197" s="4"/>
+      <c r="Y197" s="4"/>
+      <c r="Z197" s="4"/>
+    </row>
+    <row r="198" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A198" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="B198" s="6" t="s">
+      <c r="B198" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
-      <c r="L198" s="6"/>
-      <c r="M198" s="6"/>
-      <c r="N198" s="6"/>
-      <c r="O198" s="6"/>
-      <c r="P198" s="6"/>
-      <c r="Q198" s="6"/>
-      <c r="R198" s="6"/>
-      <c r="S198" s="6"/>
-      <c r="T198" s="6"/>
-      <c r="U198" s="6"/>
-      <c r="V198" s="6"/>
-      <c r="W198" s="6"/>
-      <c r="X198" s="6"/>
-      <c r="Y198" s="6"/>
-      <c r="Z198" s="6"/>
-    </row>
-    <row r="199" spans="1:26" ht="12.5">
-      <c r="A199" s="10" t="s">
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
+      <c r="H198" s="4"/>
+      <c r="I198" s="4"/>
+      <c r="J198" s="4"/>
+      <c r="K198" s="4"/>
+      <c r="L198" s="4"/>
+      <c r="M198" s="4"/>
+      <c r="N198" s="4"/>
+      <c r="O198" s="4"/>
+      <c r="P198" s="4"/>
+      <c r="Q198" s="4"/>
+      <c r="R198" s="4"/>
+      <c r="S198" s="4"/>
+      <c r="T198" s="4"/>
+      <c r="U198" s="4"/>
+      <c r="V198" s="4"/>
+      <c r="W198" s="4"/>
+      <c r="X198" s="4"/>
+      <c r="Y198" s="4"/>
+      <c r="Z198" s="4"/>
+    </row>
+    <row r="199" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A199" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="B199" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="6"/>
-      <c r="K199" s="6"/>
-      <c r="L199" s="6"/>
-      <c r="M199" s="6"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="6"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="6"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="6"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-    </row>
-    <row r="200" spans="1:26" ht="12.5">
-      <c r="A200" s="1" t="s">
+      <c r="C199" s="4"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
+      <c r="I199" s="4"/>
+      <c r="J199" s="4"/>
+      <c r="K199" s="4"/>
+      <c r="L199" s="4"/>
+      <c r="M199" s="4"/>
+      <c r="N199" s="4"/>
+      <c r="O199" s="4"/>
+      <c r="P199" s="4"/>
+      <c r="Q199" s="4"/>
+      <c r="R199" s="4"/>
+      <c r="S199" s="4"/>
+      <c r="T199" s="4"/>
+      <c r="U199" s="4"/>
+      <c r="V199" s="4"/>
+      <c r="W199" s="4"/>
+      <c r="X199" s="4"/>
+      <c r="Y199" s="4"/>
+      <c r="Z199" s="4"/>
+    </row>
+    <row r="200" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A200" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="B200" s="10" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="201" spans="1:26" ht="12.5">
-      <c r="A201" s="1" t="s">
+    <row r="201" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A201" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="B201" s="10" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="202" spans="1:26" ht="12.5">
-      <c r="A202" s="1" t="s">
+    <row r="202" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A202" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="B202" s="10" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="203" spans="1:26" ht="12.5">
-      <c r="A203" s="1" t="s">
+    <row r="203" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A203" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="B203" s="10" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="204" spans="1:26" ht="12.5">
-      <c r="A204" s="6" t="s">
+    <row r="204" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A204" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B204" s="6" t="s">
+      <c r="B204" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="6"/>
-      <c r="L204" s="6"/>
-      <c r="M204" s="6"/>
-      <c r="N204" s="6"/>
-      <c r="O204" s="6"/>
-      <c r="P204" s="6"/>
-      <c r="Q204" s="6"/>
-      <c r="R204" s="6"/>
-      <c r="S204" s="6"/>
-      <c r="T204" s="6"/>
-      <c r="U204" s="6"/>
-      <c r="V204" s="6"/>
-      <c r="W204" s="6"/>
-      <c r="X204" s="6"/>
-      <c r="Y204" s="6"/>
-      <c r="Z204" s="6"/>
-    </row>
-    <row r="205" spans="1:26" ht="12.5">
-      <c r="A205" s="1" t="s">
+      <c r="C204" s="4"/>
+      <c r="D204" s="4"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4"/>
+      <c r="G204" s="4"/>
+      <c r="H204" s="4"/>
+      <c r="I204" s="4"/>
+      <c r="J204" s="4"/>
+      <c r="K204" s="4"/>
+      <c r="L204" s="4"/>
+      <c r="M204" s="4"/>
+      <c r="N204" s="4"/>
+      <c r="O204" s="4"/>
+      <c r="P204" s="4"/>
+      <c r="Q204" s="4"/>
+      <c r="R204" s="4"/>
+      <c r="S204" s="4"/>
+      <c r="T204" s="4"/>
+      <c r="U204" s="4"/>
+      <c r="V204" s="4"/>
+      <c r="W204" s="4"/>
+      <c r="X204" s="4"/>
+      <c r="Y204" s="4"/>
+      <c r="Z204" s="4"/>
+    </row>
+    <row r="205" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A205" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="B205" s="10" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="206" spans="1:26" ht="12.5">
-      <c r="A206" s="6" t="s">
+    <row r="206" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A206" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="B206" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
-      <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="6"/>
-      <c r="J206" s="6"/>
-      <c r="K206" s="6"/>
-      <c r="L206" s="6"/>
-      <c r="M206" s="6"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="6"/>
-      <c r="Q206" s="6"/>
-      <c r="R206" s="6"/>
-      <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="6"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-    </row>
-    <row r="207" spans="1:26" ht="12.5">
-      <c r="A207" s="6" t="s">
+      <c r="C206" s="4"/>
+      <c r="D206" s="4"/>
+      <c r="E206" s="4"/>
+      <c r="F206" s="4"/>
+      <c r="G206" s="4"/>
+      <c r="H206" s="4"/>
+      <c r="I206" s="4"/>
+      <c r="J206" s="4"/>
+      <c r="K206" s="4"/>
+      <c r="L206" s="4"/>
+      <c r="M206" s="4"/>
+      <c r="N206" s="4"/>
+      <c r="O206" s="4"/>
+      <c r="P206" s="4"/>
+      <c r="Q206" s="4"/>
+      <c r="R206" s="4"/>
+      <c r="S206" s="4"/>
+      <c r="T206" s="4"/>
+      <c r="U206" s="4"/>
+      <c r="V206" s="4"/>
+      <c r="W206" s="4"/>
+      <c r="X206" s="4"/>
+      <c r="Y206" s="4"/>
+      <c r="Z206" s="4"/>
+    </row>
+    <row r="207" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A207" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="B207" s="6" t="s">
+      <c r="B207" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
-      <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
-      <c r="J207" s="6"/>
-      <c r="K207" s="6"/>
-      <c r="L207" s="6"/>
-      <c r="M207" s="6"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="6"/>
-      <c r="Q207" s="6"/>
-      <c r="R207" s="6"/>
-      <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="6"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-    </row>
-    <row r="208" spans="1:26" ht="12.5">
-      <c r="A208" s="1" t="s">
+      <c r="C207" s="4"/>
+      <c r="D207" s="4"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4"/>
+      <c r="G207" s="4"/>
+      <c r="H207" s="4"/>
+      <c r="I207" s="4"/>
+      <c r="J207" s="4"/>
+      <c r="K207" s="4"/>
+      <c r="L207" s="4"/>
+      <c r="M207" s="4"/>
+      <c r="N207" s="4"/>
+      <c r="O207" s="4"/>
+      <c r="P207" s="4"/>
+      <c r="Q207" s="4"/>
+      <c r="R207" s="4"/>
+      <c r="S207" s="4"/>
+      <c r="T207" s="4"/>
+      <c r="U207" s="4"/>
+      <c r="V207" s="4"/>
+      <c r="W207" s="4"/>
+      <c r="X207" s="4"/>
+      <c r="Y207" s="4"/>
+      <c r="Z207" s="4"/>
+    </row>
+    <row r="208" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A208" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="B208" s="10" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="209" spans="1:26" ht="12.5">
-      <c r="A209" s="6" t="s">
+    <row r="209" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A209" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="B209" s="6" t="s">
+      <c r="B209" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-      <c r="I209" s="6"/>
-      <c r="J209" s="6"/>
-      <c r="K209" s="6"/>
-      <c r="L209" s="6"/>
-      <c r="M209" s="6"/>
-      <c r="N209" s="6"/>
-      <c r="O209" s="6"/>
-      <c r="P209" s="6"/>
-      <c r="Q209" s="6"/>
-      <c r="R209" s="6"/>
-      <c r="S209" s="6"/>
-      <c r="T209" s="6"/>
-      <c r="U209" s="6"/>
-      <c r="V209" s="6"/>
-      <c r="W209" s="6"/>
-      <c r="X209" s="6"/>
-      <c r="Y209" s="6"/>
-      <c r="Z209" s="6"/>
-    </row>
-    <row r="210" spans="1:26" ht="12.5">
-      <c r="A210" s="1" t="s">
+      <c r="C209" s="4"/>
+      <c r="D209" s="4"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4"/>
+      <c r="G209" s="4"/>
+      <c r="H209" s="4"/>
+      <c r="I209" s="4"/>
+      <c r="J209" s="4"/>
+      <c r="K209" s="4"/>
+      <c r="L209" s="4"/>
+      <c r="M209" s="4"/>
+      <c r="N209" s="4"/>
+      <c r="O209" s="4"/>
+      <c r="P209" s="4"/>
+      <c r="Q209" s="4"/>
+      <c r="R209" s="4"/>
+      <c r="S209" s="4"/>
+      <c r="T209" s="4"/>
+      <c r="U209" s="4"/>
+      <c r="V209" s="4"/>
+      <c r="W209" s="4"/>
+      <c r="X209" s="4"/>
+      <c r="Y209" s="4"/>
+      <c r="Z209" s="4"/>
+    </row>
+    <row r="210" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A210" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="B210" s="10" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="211" spans="1:26" ht="12.5">
-      <c r="A211" s="1" t="s">
+    <row r="211" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A211" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="B211" s="10" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="212" spans="1:26" ht="12.5">
-      <c r="A212" s="1" t="s">
+    <row r="212" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A212" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="B212" s="10" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="213" spans="1:26" ht="12.5">
-      <c r="A213" s="1" t="s">
+    <row r="213" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A213" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="B213" s="10" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="214" spans="1:26" ht="12.5">
-      <c r="A214" s="1" t="s">
+    <row r="214" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A214" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="B214" s="10" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="215" spans="1:26" ht="12.5">
-      <c r="A215" s="1" t="s">
+    <row r="215" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A215" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="B215" s="10" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="216" spans="1:26" ht="12.5">
-      <c r="A216" s="6" t="s">
+    <row r="216" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A216" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="B216" s="6" t="s">
+      <c r="B216" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-      <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
-      <c r="I216" s="6"/>
-      <c r="J216" s="6"/>
-      <c r="K216" s="6"/>
-      <c r="L216" s="6"/>
-      <c r="M216" s="6"/>
-      <c r="N216" s="6"/>
-      <c r="O216" s="6"/>
-      <c r="P216" s="6"/>
-      <c r="Q216" s="6"/>
-      <c r="R216" s="6"/>
-      <c r="S216" s="6"/>
-      <c r="T216" s="6"/>
-      <c r="U216" s="6"/>
-      <c r="V216" s="6"/>
-      <c r="W216" s="6"/>
-      <c r="X216" s="6"/>
-      <c r="Y216" s="6"/>
-      <c r="Z216" s="6"/>
-    </row>
-    <row r="217" spans="1:26" ht="12.5">
-      <c r="A217" s="1" t="s">
+      <c r="C216" s="4"/>
+      <c r="D216" s="4"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4"/>
+      <c r="G216" s="4"/>
+      <c r="H216" s="4"/>
+      <c r="I216" s="4"/>
+      <c r="J216" s="4"/>
+      <c r="K216" s="4"/>
+      <c r="L216" s="4"/>
+      <c r="M216" s="4"/>
+      <c r="N216" s="4"/>
+      <c r="O216" s="4"/>
+      <c r="P216" s="4"/>
+      <c r="Q216" s="4"/>
+      <c r="R216" s="4"/>
+      <c r="S216" s="4"/>
+      <c r="T216" s="4"/>
+      <c r="U216" s="4"/>
+      <c r="V216" s="4"/>
+      <c r="W216" s="4"/>
+      <c r="X216" s="4"/>
+      <c r="Y216" s="4"/>
+      <c r="Z216" s="4"/>
+    </row>
+    <row r="217" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A217" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="B217" s="10" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="218" spans="1:26" ht="12.5">
-      <c r="A218" s="1" t="s">
+    <row r="218" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A218" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="B218" s="10" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="219" spans="1:26" ht="12.5">
-      <c r="A219" s="6" t="s">
+    <row r="219" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A219" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B219" s="6" t="s">
+      <c r="B219" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="C219" s="6"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
-      <c r="I219" s="6"/>
-      <c r="J219" s="6"/>
-      <c r="K219" s="6"/>
-      <c r="L219" s="6"/>
-      <c r="M219" s="6"/>
-      <c r="N219" s="6"/>
-      <c r="O219" s="6"/>
-      <c r="P219" s="6"/>
-      <c r="Q219" s="6"/>
-      <c r="R219" s="6"/>
-      <c r="S219" s="6"/>
-      <c r="T219" s="6"/>
-      <c r="U219" s="6"/>
-      <c r="V219" s="6"/>
-      <c r="W219" s="6"/>
-      <c r="X219" s="6"/>
-      <c r="Y219" s="6"/>
-      <c r="Z219" s="6"/>
-    </row>
-    <row r="220" spans="1:26" ht="12.5">
-      <c r="A220" s="6" t="s">
+      <c r="C219" s="4"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="4"/>
+      <c r="F219" s="4"/>
+      <c r="G219" s="4"/>
+      <c r="H219" s="4"/>
+      <c r="I219" s="4"/>
+      <c r="J219" s="4"/>
+      <c r="K219" s="4"/>
+      <c r="L219" s="4"/>
+      <c r="M219" s="4"/>
+      <c r="N219" s="4"/>
+      <c r="O219" s="4"/>
+      <c r="P219" s="4"/>
+      <c r="Q219" s="4"/>
+      <c r="R219" s="4"/>
+      <c r="S219" s="4"/>
+      <c r="T219" s="4"/>
+      <c r="U219" s="4"/>
+      <c r="V219" s="4"/>
+      <c r="W219" s="4"/>
+      <c r="X219" s="4"/>
+      <c r="Y219" s="4"/>
+      <c r="Z219" s="4"/>
+    </row>
+    <row r="220" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A220" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B220" s="6" t="s">
+      <c r="B220" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="C220" s="6"/>
-      <c r="D220" s="6"/>
-      <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
-      <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
-      <c r="I220" s="6"/>
-      <c r="J220" s="6"/>
-      <c r="K220" s="6"/>
-      <c r="L220" s="6"/>
-      <c r="M220" s="6"/>
-      <c r="N220" s="6"/>
-      <c r="O220" s="6"/>
-      <c r="P220" s="6"/>
-      <c r="Q220" s="6"/>
-      <c r="R220" s="6"/>
-      <c r="S220" s="6"/>
-      <c r="T220" s="6"/>
-      <c r="U220" s="6"/>
-      <c r="V220" s="6"/>
-      <c r="W220" s="6"/>
-      <c r="X220" s="6"/>
-      <c r="Y220" s="6"/>
-      <c r="Z220" s="6"/>
-    </row>
-    <row r="221" spans="1:26" ht="12.5">
-      <c r="A221" s="6" t="s">
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4"/>
+      <c r="G220" s="4"/>
+      <c r="H220" s="4"/>
+      <c r="I220" s="4"/>
+      <c r="J220" s="4"/>
+      <c r="K220" s="4"/>
+      <c r="L220" s="4"/>
+      <c r="M220" s="4"/>
+      <c r="N220" s="4"/>
+      <c r="O220" s="4"/>
+      <c r="P220" s="4"/>
+      <c r="Q220" s="4"/>
+      <c r="R220" s="4"/>
+      <c r="S220" s="4"/>
+      <c r="T220" s="4"/>
+      <c r="U220" s="4"/>
+      <c r="V220" s="4"/>
+      <c r="W220" s="4"/>
+      <c r="X220" s="4"/>
+      <c r="Y220" s="4"/>
+      <c r="Z220" s="4"/>
+    </row>
+    <row r="221" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A221" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B221" s="6" t="s">
+      <c r="B221" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="C221" s="6"/>
-      <c r="D221" s="6"/>
-      <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
-      <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
-      <c r="I221" s="6"/>
-      <c r="J221" s="6"/>
-      <c r="K221" s="6"/>
-      <c r="L221" s="6"/>
-      <c r="M221" s="6"/>
-      <c r="N221" s="6"/>
-      <c r="O221" s="6"/>
-      <c r="P221" s="6"/>
-      <c r="Q221" s="6"/>
-      <c r="R221" s="6"/>
-      <c r="S221" s="6"/>
-      <c r="T221" s="6"/>
-      <c r="U221" s="6"/>
-      <c r="V221" s="6"/>
-      <c r="W221" s="6"/>
-      <c r="X221" s="6"/>
-      <c r="Y221" s="6"/>
-      <c r="Z221" s="6"/>
-    </row>
-    <row r="222" spans="1:26" ht="12.5">
-      <c r="A222" s="6" t="s">
+      <c r="C221" s="4"/>
+      <c r="D221" s="4"/>
+      <c r="E221" s="4"/>
+      <c r="F221" s="4"/>
+      <c r="G221" s="4"/>
+      <c r="H221" s="4"/>
+      <c r="I221" s="4"/>
+      <c r="J221" s="4"/>
+      <c r="K221" s="4"/>
+      <c r="L221" s="4"/>
+      <c r="M221" s="4"/>
+      <c r="N221" s="4"/>
+      <c r="O221" s="4"/>
+      <c r="P221" s="4"/>
+      <c r="Q221" s="4"/>
+      <c r="R221" s="4"/>
+      <c r="S221" s="4"/>
+      <c r="T221" s="4"/>
+      <c r="U221" s="4"/>
+      <c r="V221" s="4"/>
+      <c r="W221" s="4"/>
+      <c r="X221" s="4"/>
+      <c r="Y221" s="4"/>
+      <c r="Z221" s="4"/>
+    </row>
+    <row r="222" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A222" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B222" s="6" t="s">
+      <c r="B222" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="C222" s="6"/>
-      <c r="D222" s="6"/>
-      <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
-      <c r="G222" s="6"/>
-      <c r="H222" s="6"/>
-      <c r="I222" s="6"/>
-      <c r="J222" s="6"/>
-      <c r="K222" s="6"/>
-      <c r="L222" s="6"/>
-      <c r="M222" s="6"/>
-      <c r="N222" s="6"/>
-      <c r="O222" s="6"/>
-      <c r="P222" s="6"/>
-      <c r="Q222" s="6"/>
-      <c r="R222" s="6"/>
-      <c r="S222" s="6"/>
-      <c r="T222" s="6"/>
-      <c r="U222" s="6"/>
-      <c r="V222" s="6"/>
-      <c r="W222" s="6"/>
-      <c r="X222" s="6"/>
-      <c r="Y222" s="6"/>
-      <c r="Z222" s="6"/>
-    </row>
-    <row r="223" spans="1:26" ht="12.5">
-      <c r="A223" s="6" t="s">
+      <c r="C222" s="4"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="4"/>
+      <c r="G222" s="4"/>
+      <c r="H222" s="4"/>
+      <c r="I222" s="4"/>
+      <c r="J222" s="4"/>
+      <c r="K222" s="4"/>
+      <c r="L222" s="4"/>
+      <c r="M222" s="4"/>
+      <c r="N222" s="4"/>
+      <c r="O222" s="4"/>
+      <c r="P222" s="4"/>
+      <c r="Q222" s="4"/>
+      <c r="R222" s="4"/>
+      <c r="S222" s="4"/>
+      <c r="T222" s="4"/>
+      <c r="U222" s="4"/>
+      <c r="V222" s="4"/>
+      <c r="W222" s="4"/>
+      <c r="X222" s="4"/>
+      <c r="Y222" s="4"/>
+      <c r="Z222" s="4"/>
+    </row>
+    <row r="223" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A223" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B223" s="6" t="s">
+      <c r="B223" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C223" s="6"/>
-      <c r="D223" s="6"/>
-      <c r="E223" s="6"/>
-      <c r="F223" s="6"/>
-      <c r="G223" s="6"/>
-      <c r="H223" s="6"/>
-      <c r="I223" s="6"/>
-      <c r="J223" s="6"/>
-      <c r="K223" s="6"/>
-      <c r="L223" s="6"/>
-      <c r="M223" s="6"/>
-      <c r="N223" s="6"/>
-      <c r="O223" s="6"/>
-      <c r="P223" s="6"/>
-      <c r="Q223" s="6"/>
-      <c r="R223" s="6"/>
-      <c r="S223" s="6"/>
-      <c r="T223" s="6"/>
-      <c r="U223" s="6"/>
-      <c r="V223" s="6"/>
-      <c r="W223" s="6"/>
-      <c r="X223" s="6"/>
-      <c r="Y223" s="6"/>
-      <c r="Z223" s="6"/>
-    </row>
-    <row r="224" spans="1:26" ht="12.5">
-      <c r="A224" s="6" t="s">
+      <c r="C223" s="4"/>
+      <c r="D223" s="4"/>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4"/>
+      <c r="G223" s="4"/>
+      <c r="H223" s="4"/>
+      <c r="I223" s="4"/>
+      <c r="J223" s="4"/>
+      <c r="K223" s="4"/>
+      <c r="L223" s="4"/>
+      <c r="M223" s="4"/>
+      <c r="N223" s="4"/>
+      <c r="O223" s="4"/>
+      <c r="P223" s="4"/>
+      <c r="Q223" s="4"/>
+      <c r="R223" s="4"/>
+      <c r="S223" s="4"/>
+      <c r="T223" s="4"/>
+      <c r="U223" s="4"/>
+      <c r="V223" s="4"/>
+      <c r="W223" s="4"/>
+      <c r="X223" s="4"/>
+      <c r="Y223" s="4"/>
+      <c r="Z223" s="4"/>
+    </row>
+    <row r="224" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A224" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B224" s="6" t="s">
+      <c r="B224" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C224" s="6"/>
-      <c r="D224" s="6"/>
-      <c r="E224" s="6"/>
-      <c r="F224" s="6"/>
-      <c r="G224" s="6"/>
-      <c r="H224" s="6"/>
-      <c r="I224" s="6"/>
-      <c r="J224" s="6"/>
-      <c r="K224" s="6"/>
-      <c r="L224" s="6"/>
-      <c r="M224" s="6"/>
-      <c r="N224" s="6"/>
-      <c r="O224" s="6"/>
-      <c r="P224" s="6"/>
-      <c r="Q224" s="6"/>
-      <c r="R224" s="6"/>
-      <c r="S224" s="6"/>
-      <c r="T224" s="6"/>
-      <c r="U224" s="6"/>
-      <c r="V224" s="6"/>
-      <c r="W224" s="6"/>
-      <c r="X224" s="6"/>
-      <c r="Y224" s="6"/>
-      <c r="Z224" s="6"/>
-    </row>
-    <row r="225" spans="1:26" ht="12.5">
-      <c r="A225" s="6" t="s">
+      <c r="C224" s="4"/>
+      <c r="D224" s="4"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+      <c r="G224" s="4"/>
+      <c r="H224" s="4"/>
+      <c r="I224" s="4"/>
+      <c r="J224" s="4"/>
+      <c r="K224" s="4"/>
+      <c r="L224" s="4"/>
+      <c r="M224" s="4"/>
+      <c r="N224" s="4"/>
+      <c r="O224" s="4"/>
+      <c r="P224" s="4"/>
+      <c r="Q224" s="4"/>
+      <c r="R224" s="4"/>
+      <c r="S224" s="4"/>
+      <c r="T224" s="4"/>
+      <c r="U224" s="4"/>
+      <c r="V224" s="4"/>
+      <c r="W224" s="4"/>
+      <c r="X224" s="4"/>
+      <c r="Y224" s="4"/>
+      <c r="Z224" s="4"/>
+    </row>
+    <row r="225" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A225" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="B225" s="6" t="s">
+      <c r="B225" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="C225" s="6"/>
-      <c r="D225" s="6"/>
-      <c r="E225" s="6"/>
-      <c r="F225" s="6"/>
-      <c r="G225" s="6"/>
-      <c r="H225" s="6"/>
-      <c r="I225" s="6"/>
-      <c r="J225" s="6"/>
-      <c r="K225" s="6"/>
-      <c r="L225" s="6"/>
-      <c r="M225" s="6"/>
-      <c r="N225" s="6"/>
-      <c r="O225" s="6"/>
-      <c r="P225" s="6"/>
-      <c r="Q225" s="6"/>
-      <c r="R225" s="6"/>
-      <c r="S225" s="6"/>
-      <c r="T225" s="6"/>
-      <c r="U225" s="6"/>
-      <c r="V225" s="6"/>
-      <c r="W225" s="6"/>
-      <c r="X225" s="6"/>
-      <c r="Y225" s="6"/>
-      <c r="Z225" s="6"/>
-    </row>
-    <row r="226" spans="1:26" ht="12.5">
-      <c r="A226" s="6" t="s">
+      <c r="C225" s="4"/>
+      <c r="D225" s="4"/>
+      <c r="E225" s="4"/>
+      <c r="F225" s="4"/>
+      <c r="G225" s="4"/>
+      <c r="H225" s="4"/>
+      <c r="I225" s="4"/>
+      <c r="J225" s="4"/>
+      <c r="K225" s="4"/>
+      <c r="L225" s="4"/>
+      <c r="M225" s="4"/>
+      <c r="N225" s="4"/>
+      <c r="O225" s="4"/>
+      <c r="P225" s="4"/>
+      <c r="Q225" s="4"/>
+      <c r="R225" s="4"/>
+      <c r="S225" s="4"/>
+      <c r="T225" s="4"/>
+      <c r="U225" s="4"/>
+      <c r="V225" s="4"/>
+      <c r="W225" s="4"/>
+      <c r="X225" s="4"/>
+      <c r="Y225" s="4"/>
+      <c r="Z225" s="4"/>
+    </row>
+    <row r="226" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A226" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="B226" s="6" t="s">
+      <c r="B226" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C226" s="6"/>
-      <c r="D226" s="6"/>
-      <c r="E226" s="6"/>
-      <c r="F226" s="6"/>
-      <c r="G226" s="6"/>
-      <c r="H226" s="6"/>
-      <c r="I226" s="6"/>
-      <c r="J226" s="6"/>
-      <c r="K226" s="6"/>
-      <c r="L226" s="6"/>
-      <c r="M226" s="6"/>
-      <c r="N226" s="6"/>
-      <c r="O226" s="6"/>
-      <c r="P226" s="6"/>
-      <c r="Q226" s="6"/>
-      <c r="R226" s="6"/>
-      <c r="S226" s="6"/>
-      <c r="T226" s="6"/>
-      <c r="U226" s="6"/>
-      <c r="V226" s="6"/>
-      <c r="W226" s="6"/>
-      <c r="X226" s="6"/>
-      <c r="Y226" s="6"/>
-      <c r="Z226" s="6"/>
-    </row>
-    <row r="227" spans="1:26" ht="12.5">
-      <c r="A227" s="6" t="s">
+      <c r="C226" s="4"/>
+      <c r="D226" s="4"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="4"/>
+      <c r="G226" s="4"/>
+      <c r="H226" s="4"/>
+      <c r="I226" s="4"/>
+      <c r="J226" s="4"/>
+      <c r="K226" s="4"/>
+      <c r="L226" s="4"/>
+      <c r="M226" s="4"/>
+      <c r="N226" s="4"/>
+      <c r="O226" s="4"/>
+      <c r="P226" s="4"/>
+      <c r="Q226" s="4"/>
+      <c r="R226" s="4"/>
+      <c r="S226" s="4"/>
+      <c r="T226" s="4"/>
+      <c r="U226" s="4"/>
+      <c r="V226" s="4"/>
+      <c r="W226" s="4"/>
+      <c r="X226" s="4"/>
+      <c r="Y226" s="4"/>
+      <c r="Z226" s="4"/>
+    </row>
+    <row r="227" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A227" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B227" s="6" t="s">
+      <c r="B227" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="C227" s="6"/>
-      <c r="D227" s="6"/>
-      <c r="E227" s="6"/>
-      <c r="F227" s="6"/>
-      <c r="G227" s="6"/>
-      <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
-      <c r="J227" s="6"/>
-      <c r="K227" s="6"/>
-      <c r="L227" s="6"/>
-      <c r="M227" s="6"/>
-      <c r="N227" s="6"/>
-      <c r="O227" s="6"/>
-      <c r="P227" s="6"/>
-      <c r="Q227" s="6"/>
-      <c r="R227" s="6"/>
-      <c r="S227" s="6"/>
-      <c r="T227" s="6"/>
-      <c r="U227" s="6"/>
-      <c r="V227" s="6"/>
-      <c r="W227" s="6"/>
-      <c r="X227" s="6"/>
-      <c r="Y227" s="6"/>
-      <c r="Z227" s="6"/>
-    </row>
-    <row r="228" spans="1:26" ht="12.5">
-      <c r="A228" s="6" t="s">
+      <c r="C227" s="4"/>
+      <c r="D227" s="4"/>
+      <c r="E227" s="4"/>
+      <c r="F227" s="4"/>
+      <c r="G227" s="4"/>
+      <c r="H227" s="4"/>
+      <c r="I227" s="4"/>
+      <c r="J227" s="4"/>
+      <c r="K227" s="4"/>
+      <c r="L227" s="4"/>
+      <c r="M227" s="4"/>
+      <c r="N227" s="4"/>
+      <c r="O227" s="4"/>
+      <c r="P227" s="4"/>
+      <c r="Q227" s="4"/>
+      <c r="R227" s="4"/>
+      <c r="S227" s="4"/>
+      <c r="T227" s="4"/>
+      <c r="U227" s="4"/>
+      <c r="V227" s="4"/>
+      <c r="W227" s="4"/>
+      <c r="X227" s="4"/>
+      <c r="Y227" s="4"/>
+      <c r="Z227" s="4"/>
+    </row>
+    <row r="228" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A228" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B228" s="6" t="s">
+      <c r="B228" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C228" s="6"/>
-      <c r="D228" s="6"/>
-      <c r="E228" s="6"/>
-      <c r="F228" s="6"/>
-      <c r="G228" s="6"/>
-      <c r="H228" s="6"/>
-      <c r="I228" s="6"/>
-      <c r="J228" s="6"/>
-      <c r="K228" s="6"/>
-      <c r="L228" s="6"/>
-      <c r="M228" s="6"/>
-      <c r="N228" s="6"/>
-      <c r="O228" s="6"/>
-      <c r="P228" s="6"/>
-      <c r="Q228" s="6"/>
-      <c r="R228" s="6"/>
-      <c r="S228" s="6"/>
-      <c r="T228" s="6"/>
-      <c r="U228" s="6"/>
-      <c r="V228" s="6"/>
-      <c r="W228" s="6"/>
-      <c r="X228" s="6"/>
-      <c r="Y228" s="6"/>
-      <c r="Z228" s="6"/>
-    </row>
-    <row r="229" spans="1:26" ht="12.5">
-      <c r="A229" s="1" t="s">
+      <c r="C228" s="4"/>
+      <c r="D228" s="4"/>
+      <c r="E228" s="4"/>
+      <c r="F228" s="4"/>
+      <c r="G228" s="4"/>
+      <c r="H228" s="4"/>
+      <c r="I228" s="4"/>
+      <c r="J228" s="4"/>
+      <c r="K228" s="4"/>
+      <c r="L228" s="4"/>
+      <c r="M228" s="4"/>
+      <c r="N228" s="4"/>
+      <c r="O228" s="4"/>
+      <c r="P228" s="4"/>
+      <c r="Q228" s="4"/>
+      <c r="R228" s="4"/>
+      <c r="S228" s="4"/>
+      <c r="T228" s="4"/>
+      <c r="U228" s="4"/>
+      <c r="V228" s="4"/>
+      <c r="W228" s="4"/>
+      <c r="X228" s="4"/>
+      <c r="Y228" s="4"/>
+      <c r="Z228" s="4"/>
+    </row>
+    <row r="229" spans="1:26" s="12" customFormat="1" ht="12.5">
+      <c r="A229" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="B229" s="1" t="s">
+      <c r="B229" s="10" t="s">
         <v>423</v>
       </c>
     </row>

--- a/Libro de codigos.xlsx
+++ b/Libro de codigos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luis_\Desktop\github\CATALINA_PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CCCD70-0A44-424B-A80D-79C22ACA7D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E699B3C2-D6EC-496D-9D06-03A976DE0568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -2962,7 +2962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2989,13 +2989,14 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3331,11 +3332,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="22" customFormat="1" ht="15.75" customHeight="1">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3876,11 +3877,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A50" s="23" t="s">
+    <row r="50" spans="1:26" ht="12.5">
+      <c r="A50" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="1" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4370,179 +4371,179 @@
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A76" s="24" t="s">
+    <row r="76" spans="1:26" ht="12.5">
+      <c r="A76" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="21" t="s">
+      <c r="B76" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="77" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A77" s="24" t="s">
+    <row r="77" spans="1:26" ht="12.5">
+      <c r="A77" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="78" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A78" s="24" t="s">
+    <row r="78" spans="1:26" ht="12.5">
+      <c r="A78" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="B78" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="79" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A79" s="23" t="s">
+    <row r="79" spans="1:26" ht="12.5">
+      <c r="A79" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="80" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A80" s="24" t="s">
+    <row r="80" spans="1:26" ht="12.5">
+      <c r="A80" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="B80" s="21" t="s">
+      <c r="B80" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A81" s="24" t="s">
+    <row r="81" spans="1:3" ht="12.5">
+      <c r="A81" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="B81" s="21" t="s">
+      <c r="B81" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A82" s="24" t="s">
+    <row r="82" spans="1:3" ht="12.5">
+      <c r="A82" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="83" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A83" s="24" t="s">
+    <row r="83" spans="1:3" ht="12.5">
+      <c r="A83" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="B83" s="21" t="s">
+      <c r="B83" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="84" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A84" s="24" t="s">
+    <row r="84" spans="1:3" ht="12.5">
+      <c r="A84" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="21" t="s">
+      <c r="B84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="85" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A85" s="24" t="s">
+    <row r="85" spans="1:3" ht="12.5">
+      <c r="A85" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="21" t="s">
+      <c r="B85" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="21" t="s">
+      <c r="C85" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A86" s="24" t="s">
+    <row r="86" spans="1:3" ht="12.5">
+      <c r="A86" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="B86" s="21" t="s">
+      <c r="B86" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="21" t="s">
+      <c r="C86" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A87" s="23" t="s">
+    <row r="87" spans="1:3" ht="12.5">
+      <c r="A87" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B87" s="21" t="s">
+      <c r="B87" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C87" s="21" t="s">
+      <c r="C87" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="88" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A88" s="23" t="s">
+    <row r="88" spans="1:3" ht="12.5">
+      <c r="A88" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B88" s="21" t="s">
+      <c r="B88" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C88" s="21" t="s">
+      <c r="C88" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A89" s="23" t="s">
+    <row r="89" spans="1:3" ht="12.5">
+      <c r="A89" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B89" s="21" t="s">
+      <c r="B89" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="90" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A90" s="23" t="s">
+    <row r="90" spans="1:3" ht="12.5">
+      <c r="A90" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B90" s="21" t="s">
+      <c r="B90" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C90" s="21" t="s">
+      <c r="C90" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="91" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A91" s="23" t="s">
+    <row r="91" spans="1:3" ht="12.5">
+      <c r="A91" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B91" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A92" s="23" t="s">
+    <row r="92" spans="1:3" ht="12.5">
+      <c r="A92" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C92" s="21" t="s">
+      <c r="C92" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A93" s="23" t="s">
+    <row r="93" spans="1:3" ht="12.5">
+      <c r="A93" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="B93" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="94" spans="1:3" s="12" customFormat="1" ht="12.5">
-      <c r="A94" s="17" t="s">
+    <row r="94" spans="1:3" s="25" customFormat="1" ht="12.5">
+      <c r="A94" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" s="24" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4554,155 +4555,155 @@
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:3" s="22" customFormat="1" ht="12.5">
-      <c r="A96" s="23" t="s">
+    <row r="96" spans="1:3" ht="12.5">
+      <c r="A96" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A97" s="23" t="s">
+    <row r="97" spans="1:2" ht="12.5">
+      <c r="A97" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="B97" s="21" t="s">
+      <c r="B97" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="98" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A98" s="23" t="s">
+    <row r="98" spans="1:2" ht="12.5">
+      <c r="A98" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="B98" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="99" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A99" s="23" t="s">
+    <row r="99" spans="1:2" ht="12.5">
+      <c r="A99" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="21" t="s">
+      <c r="B99" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="100" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A100" s="24" t="s">
+    <row r="100" spans="1:2" ht="12.5">
+      <c r="A100" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="B100" s="21" t="s">
+      <c r="B100" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="101" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A101" s="24" t="s">
+    <row r="101" spans="1:2" ht="12.5">
+      <c r="A101" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="102" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A102" s="24" t="s">
+    <row r="102" spans="1:2" ht="12.5">
+      <c r="A102" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="103" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A103" s="24" t="s">
+    <row r="103" spans="1:2" ht="12.5">
+      <c r="A103" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="B103" s="21" t="s">
+      <c r="B103" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A104" s="24" t="s">
+    <row r="104" spans="1:2" ht="12.5">
+      <c r="A104" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="B104" s="21" t="s">
+      <c r="B104" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="105" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A105" s="24" t="s">
+    <row r="105" spans="1:2" ht="12.5">
+      <c r="A105" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="106" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A106" s="24" t="s">
+    <row r="106" spans="1:2" ht="12.5">
+      <c r="A106" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B106" s="21" t="s">
+      <c r="B106" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A107" s="23" t="s">
+    <row r="107" spans="1:2" ht="12.5">
+      <c r="A107" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="B107" s="21" t="s">
+      <c r="B107" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="108" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A108" s="23" t="s">
+    <row r="108" spans="1:2" ht="12.5">
+      <c r="A108" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="109" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A109" s="23" t="s">
+    <row r="109" spans="1:2" ht="12.5">
+      <c r="A109" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="B109" s="21" t="s">
+      <c r="B109" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="110" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A110" s="23" t="s">
+    <row r="110" spans="1:2" ht="12.5">
+      <c r="A110" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B110" s="21" t="s">
+      <c r="B110" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="111" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A111" s="23" t="s">
+    <row r="111" spans="1:2" ht="12.5">
+      <c r="A111" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B111" s="21" t="s">
+      <c r="B111" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="112" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A112" s="23" t="s">
+    <row r="112" spans="1:2" ht="12.5">
+      <c r="A112" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="B112" s="21" t="s">
+      <c r="B112" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="113" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A113" s="23" t="s">
+    <row r="113" spans="1:2" ht="12.5">
+      <c r="A113" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B113" s="21" t="s">
+      <c r="B113" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="114" spans="1:2" s="12" customFormat="1" ht="12.5">
-      <c r="A114" s="17" t="s">
+    <row r="114" spans="1:2" s="25" customFormat="1" ht="12.5">
+      <c r="A114" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B114" s="24" t="s">
         <v>169</v>
       </c>
     </row>
@@ -4714,147 +4715,147 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A116" s="24" t="s">
+    <row r="116" spans="1:2" ht="12.5">
+      <c r="A116" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="B116" s="21" t="s">
+      <c r="B116" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="117" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A117" s="24" t="s">
+    <row r="117" spans="1:2" ht="12.5">
+      <c r="A117" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="B117" s="21" t="s">
+      <c r="B117" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="118" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A118" s="24" t="s">
+    <row r="118" spans="1:2" ht="12.5">
+      <c r="A118" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="B118" s="21" t="s">
+      <c r="B118" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="119" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A119" s="23" t="s">
+    <row r="119" spans="1:2" ht="12.5">
+      <c r="A119" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="B119" s="21" t="s">
+      <c r="B119" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="120" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A120" s="24" t="s">
+    <row r="120" spans="1:2" ht="12.5">
+      <c r="A120" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="B120" s="21" t="s">
+      <c r="B120" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="121" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A121" s="24" t="s">
+    <row r="121" spans="1:2" ht="12.5">
+      <c r="A121" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="B121" s="21" t="s">
+      <c r="B121" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="122" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A122" s="24" t="s">
+    <row r="122" spans="1:2" ht="12.5">
+      <c r="A122" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="B122" s="21" t="s">
+      <c r="B122" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="123" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A123" s="24" t="s">
+    <row r="123" spans="1:2" ht="12.5">
+      <c r="A123" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="B123" s="21" t="s">
+      <c r="B123" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="124" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A124" s="24" t="s">
+    <row r="124" spans="1:2" ht="12.5">
+      <c r="A124" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="B124" s="21" t="s">
+      <c r="B124" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="125" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A125" s="24" t="s">
+    <row r="125" spans="1:2" ht="12.5">
+      <c r="A125" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B125" s="21" t="s">
+      <c r="B125" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="126" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A126" s="24" t="s">
+    <row r="126" spans="1:2" ht="12.5">
+      <c r="A126" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="B126" s="21" t="s">
+      <c r="B126" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A127" s="23" t="s">
+    <row r="127" spans="1:2" ht="12.5">
+      <c r="A127" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B127" s="21" t="s">
+      <c r="B127" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="128" spans="1:2" s="22" customFormat="1" ht="12.5">
-      <c r="A128" s="23" t="s">
+    <row r="128" spans="1:2" ht="12.5">
+      <c r="A128" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B128" s="21" t="s">
+      <c r="B128" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="129" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A129" s="23" t="s">
+    <row r="129" spans="1:26" ht="12.5">
+      <c r="A129" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B129" s="21" t="s">
+      <c r="B129" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="130" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A130" s="23" t="s">
+    <row r="130" spans="1:26" ht="12.5">
+      <c r="A130" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="B130" s="21" t="s">
+      <c r="B130" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A131" s="23" t="s">
+    <row r="131" spans="1:26" ht="12.5">
+      <c r="A131" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="B131" s="21" t="s">
+      <c r="B131" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A132" s="23" t="s">
+    <row r="132" spans="1:26" ht="12.5">
+      <c r="A132" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="B132" s="21" t="s">
+      <c r="B132" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="133" spans="1:26" s="22" customFormat="1" ht="12.5">
-      <c r="A133" s="23" t="s">
+    <row r="133" spans="1:26" ht="12.5">
+      <c r="A133" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B133" s="21" t="s">
+      <c r="B133" s="1" t="s">
         <v>167</v>
       </c>
     </row>
